--- a/research/traditional_assets/database/data/south_africa/south_africa_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_auto_parts.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.145215074901648</v>
+        <v>0.1448558441994136</v>
       </c>
       <c r="C2">
-        <v>328.241450422994</v>
+        <v>325.7626697480222</v>
       </c>
       <c r="D2">
-        <v>270.841450422994</v>
+        <v>271.8236697480223</v>
       </c>
       <c r="E2">
-        <v>-244.8</v>
+        <v>-241.339</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="G2">
         <v>57.4</v>
@@ -1445,28 +1445,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1740883</v>
       </c>
       <c r="N2">
-        <v>70.40000000000001</v>
+        <v>70.22591170000001</v>
       </c>
       <c r="O2">
-        <v>19.008</v>
+        <v>18.960996159</v>
       </c>
       <c r="P2">
-        <v>51.392</v>
+        <v>51.26491554100001</v>
       </c>
       <c r="Q2">
-        <v>73.792</v>
+        <v>73.664915541</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.145215074901648</v>
+        <v>0.1459481355549632</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.199748858231027</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>404.3924835844799</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1448558441994136</v>
+        <v>0.1444966134971791</v>
       </c>
       <c r="C3">
-        <v>325.7626697480222</v>
+        <v>323.2910391327206</v>
       </c>
       <c r="D3">
-        <v>271.8236697480223</v>
+        <v>272.8130391327207</v>
       </c>
       <c r="E3">
-        <v>-241.339</v>
+        <v>-237.878</v>
       </c>
       <c r="F3">
-        <v>3.461</v>
+        <v>6.922000000000001</v>
       </c>
       <c r="G3">
         <v>57.4</v>
@@ -1527,28 +1527,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M3">
-        <v>0.1740883</v>
+        <v>0.3481766</v>
       </c>
       <c r="N3">
-        <v>70.22591170000001</v>
+        <v>70.0518234</v>
       </c>
       <c r="O3">
-        <v>18.960996159</v>
+        <v>18.913992318</v>
       </c>
       <c r="P3">
-        <v>51.26491554100001</v>
+        <v>51.13783108200001</v>
       </c>
       <c r="Q3">
-        <v>73.664915541</v>
+        <v>73.537831082</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1459481355549632</v>
+        <v>0.1466961566297746</v>
       </c>
       <c r="T3">
-        <v>1.199748858231027</v>
+        <v>1.208709957960589</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>404.3924835844799</v>
+        <v>202.1962417922399</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1444966134971791</v>
+        <v>0.1441373827949446</v>
       </c>
       <c r="C4">
-        <v>323.2910391327206</v>
+        <v>320.8266369355189</v>
       </c>
       <c r="D4">
-        <v>272.8130391327207</v>
+        <v>273.8096369355189</v>
       </c>
       <c r="E4">
-        <v>-237.878</v>
+        <v>-234.417</v>
       </c>
       <c r="F4">
-        <v>6.922000000000001</v>
+        <v>10.383</v>
       </c>
       <c r="G4">
         <v>57.4</v>
@@ -1609,28 +1609,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M4">
-        <v>0.3481766</v>
+        <v>0.5222649</v>
       </c>
       <c r="N4">
-        <v>70.0518234</v>
+        <v>69.87773510000001</v>
       </c>
       <c r="O4">
-        <v>18.913992318</v>
+        <v>18.866988477</v>
       </c>
       <c r="P4">
-        <v>51.13783108200001</v>
+        <v>51.010746623</v>
       </c>
       <c r="Q4">
-        <v>73.537831082</v>
+        <v>73.41074662299999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1466961566297746</v>
+        <v>0.1474596008195306</v>
       </c>
       <c r="T4">
-        <v>1.208709957960589</v>
+        <v>1.217855822633029</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>202.1962417922399</v>
+        <v>134.7974945281599</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1441373827949446</v>
+        <v>0.1437781520927102</v>
       </c>
       <c r="C5">
-        <v>320.8266369355189</v>
+        <v>318.369542664031</v>
       </c>
       <c r="D5">
-        <v>273.8096369355189</v>
+        <v>274.813542664031</v>
       </c>
       <c r="E5">
-        <v>-234.417</v>
+        <v>-230.956</v>
       </c>
       <c r="F5">
-        <v>10.383</v>
+        <v>13.844</v>
       </c>
       <c r="G5">
         <v>57.4</v>
@@ -1691,28 +1691,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M5">
-        <v>0.5222649</v>
+        <v>0.6963532</v>
       </c>
       <c r="N5">
-        <v>69.87773510000001</v>
+        <v>69.7036468</v>
       </c>
       <c r="O5">
-        <v>18.866988477</v>
+        <v>18.819984636</v>
       </c>
       <c r="P5">
-        <v>51.010746623</v>
+        <v>50.883662164</v>
       </c>
       <c r="Q5">
-        <v>73.41074662299999</v>
+        <v>73.28366216399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1474596008195306</v>
+        <v>0.1482389500965731</v>
       </c>
       <c r="T5">
-        <v>1.217855822633029</v>
+        <v>1.227192226152811</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>134.7974945281599</v>
+        <v>101.09812089612</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1437781520927102</v>
+        <v>0.1434189213904757</v>
       </c>
       <c r="C6">
-        <v>318.369542664031</v>
+        <v>315.919836996201</v>
       </c>
       <c r="D6">
-        <v>274.813542664031</v>
+        <v>275.824836996201</v>
       </c>
       <c r="E6">
-        <v>-230.956</v>
+        <v>-227.495</v>
       </c>
       <c r="F6">
-        <v>13.844</v>
+        <v>17.305</v>
       </c>
       <c r="G6">
         <v>57.4</v>
@@ -1773,28 +1773,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M6">
-        <v>0.6963532</v>
+        <v>0.8704415000000001</v>
       </c>
       <c r="N6">
-        <v>69.7036468</v>
+        <v>69.52955850000001</v>
       </c>
       <c r="O6">
-        <v>18.819984636</v>
+        <v>18.772980795</v>
       </c>
       <c r="P6">
-        <v>50.883662164</v>
+        <v>50.75657770500001</v>
       </c>
       <c r="Q6">
-        <v>73.28366216399999</v>
+        <v>73.156577705</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1482389500965731</v>
+        <v>0.1490347067268166</v>
       </c>
       <c r="T6">
-        <v>1.227192226152811</v>
+        <v>1.236725185536167</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>101.09812089612</v>
+        <v>80.87849671689597</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1434189213904757</v>
+        <v>0.1430596906882413</v>
       </c>
       <c r="C7">
-        <v>315.919836996201</v>
+        <v>313.4776018019153</v>
       </c>
       <c r="D7">
-        <v>275.824836996201</v>
+        <v>276.8436018019154</v>
       </c>
       <c r="E7">
-        <v>-227.495</v>
+        <v>-224.034</v>
       </c>
       <c r="F7">
-        <v>17.305</v>
+        <v>20.766</v>
       </c>
       <c r="G7">
         <v>57.4</v>
@@ -1855,28 +1855,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M7">
-        <v>0.8704415000000001</v>
+        <v>1.0445298</v>
       </c>
       <c r="N7">
-        <v>69.52955850000001</v>
+        <v>69.3554702</v>
       </c>
       <c r="O7">
-        <v>18.772980795</v>
+        <v>18.725976954</v>
       </c>
       <c r="P7">
-        <v>50.75657770500001</v>
+        <v>50.629493246</v>
       </c>
       <c r="Q7">
-        <v>73.156577705</v>
+        <v>73.02949324599999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1490347067268166</v>
+        <v>0.1498473943491929</v>
       </c>
       <c r="T7">
-        <v>1.236725185536167</v>
+        <v>1.246460973842574</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.87849671689597</v>
+        <v>67.39874726407997</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1430596906882413</v>
+        <v>0.1427004599860069</v>
       </c>
       <c r="C8">
-        <v>313.4776018019153</v>
+        <v>311.0429201650973</v>
       </c>
       <c r="D8">
-        <v>276.8436018019154</v>
+        <v>277.8699201650973</v>
       </c>
       <c r="E8">
-        <v>-224.034</v>
+        <v>-220.573</v>
       </c>
       <c r="F8">
-        <v>20.766</v>
+        <v>24.227</v>
       </c>
       <c r="G8">
         <v>57.4</v>
@@ -1937,28 +1937,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M8">
-        <v>1.0445298</v>
+        <v>1.2186181</v>
       </c>
       <c r="N8">
-        <v>69.3554702</v>
+        <v>69.18138190000001</v>
       </c>
       <c r="O8">
-        <v>18.725976954</v>
+        <v>18.678973113</v>
       </c>
       <c r="P8">
-        <v>50.629493246</v>
+        <v>50.50240878700001</v>
       </c>
       <c r="Q8">
-        <v>73.02949324599999</v>
+        <v>72.90240878700001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1498473943491929</v>
+        <v>0.1506775591247386</v>
       </c>
       <c r="T8">
-        <v>1.246460973842574</v>
+        <v>1.256406133940517</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>67.39874726407997</v>
+        <v>57.77035479778284</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1427004599860069</v>
+        <v>0.1423412292837724</v>
       </c>
       <c r="C9">
-        <v>311.0429201650974</v>
+        <v>308.6158764062938</v>
       </c>
       <c r="D9">
-        <v>277.8699201650974</v>
+        <v>278.9038764062938</v>
       </c>
       <c r="E9">
-        <v>-220.573</v>
+        <v>-217.112</v>
       </c>
       <c r="F9">
-        <v>24.227</v>
+        <v>27.688</v>
       </c>
       <c r="G9">
         <v>57.4</v>
@@ -2019,28 +2019,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M9">
-        <v>1.2186181</v>
+        <v>1.3927064</v>
       </c>
       <c r="N9">
-        <v>69.18138190000001</v>
+        <v>69.00729360000001</v>
       </c>
       <c r="O9">
-        <v>18.678973113</v>
+        <v>18.631969272</v>
       </c>
       <c r="P9">
-        <v>50.50240878700001</v>
+        <v>50.375324328</v>
       </c>
       <c r="Q9">
-        <v>72.90240878700001</v>
+        <v>72.77532432800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1506775591247386</v>
+        <v>0.1515257709606222</v>
       </c>
       <c r="T9">
-        <v>1.256406133940517</v>
+        <v>1.266567493171023</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.77035479778284</v>
+        <v>50.54906044805999</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1423412292837724</v>
+        <v>0.1419819985815379</v>
       </c>
       <c r="C10">
-        <v>308.6158764062938</v>
+        <v>306.1965561057691</v>
       </c>
       <c r="D10">
-        <v>278.9038764062938</v>
+        <v>279.9455561057691</v>
       </c>
       <c r="E10">
-        <v>-217.112</v>
+        <v>-213.651</v>
       </c>
       <c r="F10">
-        <v>27.688</v>
+        <v>31.149</v>
       </c>
       <c r="G10">
         <v>57.4</v>
@@ -2101,28 +2101,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M10">
-        <v>1.3927064</v>
+        <v>1.5667947</v>
       </c>
       <c r="N10">
-        <v>69.00729360000001</v>
+        <v>68.8332053</v>
       </c>
       <c r="O10">
-        <v>18.631969272</v>
+        <v>18.584965431</v>
       </c>
       <c r="P10">
-        <v>50.375324328</v>
+        <v>50.248239869</v>
       </c>
       <c r="Q10">
-        <v>72.77532432800001</v>
+        <v>72.64823986900001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1515257709606222</v>
+        <v>0.1523926248148769</v>
       </c>
       <c r="T10">
-        <v>1.266567493171023</v>
+        <v>1.276952178978024</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.54906044805999</v>
+        <v>44.93249817605331</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1419819985815379</v>
+        <v>0.1416227678793035</v>
       </c>
       <c r="C11">
-        <v>306.1965561057691</v>
+        <v>303.7850461271171</v>
       </c>
       <c r="D11">
-        <v>279.9455561057691</v>
+        <v>280.9950461271171</v>
       </c>
       <c r="E11">
-        <v>-213.651</v>
+        <v>-210.19</v>
       </c>
       <c r="F11">
-        <v>31.149</v>
+        <v>34.61</v>
       </c>
       <c r="G11">
         <v>57.4</v>
@@ -2183,28 +2183,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M11">
-        <v>1.5667947</v>
+        <v>1.740883</v>
       </c>
       <c r="N11">
-        <v>68.8332053</v>
+        <v>68.65911700000001</v>
       </c>
       <c r="O11">
-        <v>18.584965431</v>
+        <v>18.53796159000001</v>
       </c>
       <c r="P11">
-        <v>50.248239869</v>
+        <v>50.12115541</v>
       </c>
       <c r="Q11">
-        <v>72.64823986900001</v>
+        <v>72.52115541000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1523926248148769</v>
+        <v>0.153278742088115</v>
       </c>
       <c r="T11">
-        <v>1.276952178978024</v>
+        <v>1.287567635580736</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.93249817605331</v>
+        <v>40.43924835844799</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1416227678793035</v>
+        <v>0.141263537177069</v>
       </c>
       <c r="C12">
-        <v>303.7850461271171</v>
+        <v>301.3814346414084</v>
       </c>
       <c r="D12">
-        <v>280.9950461271171</v>
+        <v>282.0524346414085</v>
       </c>
       <c r="E12">
-        <v>-210.19</v>
+        <v>-206.729</v>
       </c>
       <c r="F12">
-        <v>34.61000000000001</v>
+        <v>38.07100000000001</v>
       </c>
       <c r="G12">
         <v>57.4</v>
@@ -2265,28 +2265,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M12">
-        <v>1.740883</v>
+        <v>1.9149713</v>
       </c>
       <c r="N12">
-        <v>68.65911700000001</v>
+        <v>68.4850287</v>
       </c>
       <c r="O12">
-        <v>18.53796159000001</v>
+        <v>18.490957749</v>
       </c>
       <c r="P12">
-        <v>50.12115541</v>
+        <v>49.994070951</v>
       </c>
       <c r="Q12">
-        <v>72.52115541000001</v>
+        <v>72.394070951</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.153278742088115</v>
+        <v>0.1541847721090664</v>
       </c>
       <c r="T12">
-        <v>1.287567635580736</v>
+        <v>1.298421641770026</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.43924835844798</v>
+        <v>36.76295305313453</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.141263537177069</v>
+        <v>0.1409043064748346</v>
       </c>
       <c r="C13">
-        <v>301.3814346414084</v>
+        <v>298.985811151882</v>
       </c>
       <c r="D13">
-        <v>282.0524346414085</v>
+        <v>283.117811151882</v>
       </c>
       <c r="E13">
-        <v>-206.729</v>
+        <v>-203.268</v>
       </c>
       <c r="F13">
-        <v>38.07100000000001</v>
+        <v>41.532</v>
       </c>
       <c r="G13">
         <v>57.4</v>
@@ -2347,28 +2347,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M13">
-        <v>1.9149713</v>
+        <v>2.0890596</v>
       </c>
       <c r="N13">
-        <v>68.4850287</v>
+        <v>68.31094040000001</v>
       </c>
       <c r="O13">
-        <v>18.490957749</v>
+        <v>18.443953908</v>
       </c>
       <c r="P13">
-        <v>49.994070951</v>
+        <v>49.866986492</v>
       </c>
       <c r="Q13">
-        <v>72.394070951</v>
+        <v>72.266986492</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1541847721090664</v>
+        <v>0.155111393721403</v>
       </c>
       <c r="T13">
-        <v>1.298421641770026</v>
+        <v>1.309522329918163</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.76295305313453</v>
+        <v>33.69937363203999</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1409043064748346</v>
+        <v>0.1405450757726002</v>
       </c>
       <c r="C14">
-        <v>298.985811151882</v>
+        <v>296.5982665192013</v>
       </c>
       <c r="D14">
-        <v>283.117811151882</v>
+        <v>284.1912665192013</v>
       </c>
       <c r="E14">
-        <v>-203.268</v>
+        <v>-199.807</v>
       </c>
       <c r="F14">
-        <v>41.532</v>
+        <v>44.993</v>
       </c>
       <c r="G14">
         <v>57.4</v>
@@ -2429,28 +2429,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M14">
-        <v>2.0890596</v>
+        <v>2.2631479</v>
       </c>
       <c r="N14">
-        <v>68.31094040000001</v>
+        <v>68.1368521</v>
       </c>
       <c r="O14">
-        <v>18.443953908</v>
+        <v>18.396950067</v>
       </c>
       <c r="P14">
-        <v>49.866986492</v>
+        <v>49.73990203299999</v>
       </c>
       <c r="Q14">
-        <v>72.266986492</v>
+        <v>72.139902033</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.155111393721403</v>
+        <v>0.1560593169800002</v>
       </c>
       <c r="T14">
-        <v>1.309522329918163</v>
+        <v>1.320878206299591</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.69937363203999</v>
+        <v>31.10711412188306</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1405450757726002</v>
+        <v>0.1401858450703657</v>
       </c>
       <c r="C15">
-        <v>296.5982665192013</v>
+        <v>294.2188929872854</v>
       </c>
       <c r="D15">
-        <v>284.1912665192013</v>
+        <v>285.2728929872854</v>
       </c>
       <c r="E15">
-        <v>-199.807</v>
+        <v>-196.346</v>
       </c>
       <c r="F15">
-        <v>44.993</v>
+        <v>48.45400000000001</v>
       </c>
       <c r="G15">
         <v>57.4</v>
@@ -2511,28 +2511,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M15">
-        <v>2.2631479</v>
+        <v>2.4372362</v>
       </c>
       <c r="N15">
-        <v>68.1368521</v>
+        <v>67.9627638</v>
       </c>
       <c r="O15">
-        <v>18.396950067</v>
+        <v>18.349946226</v>
       </c>
       <c r="P15">
-        <v>49.73990203299999</v>
+        <v>49.612817574</v>
       </c>
       <c r="Q15">
-        <v>72.139902033</v>
+        <v>72.012817574</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1560593169800002</v>
+        <v>0.1570292849655415</v>
       </c>
       <c r="T15">
-        <v>1.320878206299591</v>
+        <v>1.332498172829424</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.10711412188306</v>
+        <v>28.88517739889142</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1401858450703657</v>
+        <v>0.1398266143681313</v>
       </c>
       <c r="C16">
-        <v>294.2188929872854</v>
+        <v>291.8477842097327</v>
       </c>
       <c r="D16">
-        <v>285.2728929872854</v>
+        <v>286.3627842097327</v>
       </c>
       <c r="E16">
-        <v>-196.346</v>
+        <v>-192.885</v>
       </c>
       <c r="F16">
-        <v>48.45400000000001</v>
+        <v>51.91500000000001</v>
       </c>
       <c r="G16">
         <v>57.4</v>
@@ -2593,28 +2593,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M16">
-        <v>2.4372362</v>
+        <v>2.611324500000001</v>
       </c>
       <c r="N16">
-        <v>67.9627638</v>
+        <v>67.78867550000001</v>
       </c>
       <c r="O16">
-        <v>18.349946226</v>
+        <v>18.30294238500001</v>
       </c>
       <c r="P16">
-        <v>49.612817574</v>
+        <v>49.485733115</v>
       </c>
       <c r="Q16">
-        <v>72.012817574</v>
+        <v>71.88573311499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1570292849655415</v>
+        <v>0.1580220757272133</v>
       </c>
       <c r="T16">
-        <v>1.332498172829424</v>
+        <v>1.34439155033643</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.88517739889142</v>
+        <v>26.95949890563199</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1398266143681313</v>
+        <v>0.1394673836658968</v>
       </c>
       <c r="C17">
-        <v>291.8477842097327</v>
+        <v>289.4850352768535</v>
       </c>
       <c r="D17">
-        <v>286.3627842097327</v>
+        <v>287.4610352768535</v>
       </c>
       <c r="E17">
-        <v>-192.885</v>
+        <v>-189.424</v>
       </c>
       <c r="F17">
-        <v>51.915</v>
+        <v>55.376</v>
       </c>
       <c r="G17">
         <v>57.4</v>
@@ -2675,28 +2675,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M17">
-        <v>2.6113245</v>
+        <v>2.7854128</v>
       </c>
       <c r="N17">
-        <v>67.78867550000001</v>
+        <v>67.6145872</v>
       </c>
       <c r="O17">
-        <v>18.30294238500001</v>
+        <v>18.255938544</v>
       </c>
       <c r="P17">
-        <v>49.485733115</v>
+        <v>49.358648656</v>
       </c>
       <c r="Q17">
-        <v>71.88573311499999</v>
+        <v>71.75864865599999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1580220757272133</v>
+        <v>0.1590385043641629</v>
       </c>
       <c r="T17">
-        <v>1.34439155033643</v>
+        <v>1.356568103498365</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.959498905632</v>
+        <v>25.27453022402999</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1394673836658968</v>
+        <v>0.1391081529636624</v>
       </c>
       <c r="C18">
-        <v>289.4850352768535</v>
+        <v>287.130742743325</v>
       </c>
       <c r="D18">
-        <v>287.4610352768535</v>
+        <v>288.567742743325</v>
       </c>
       <c r="E18">
-        <v>-189.424</v>
+        <v>-185.963</v>
       </c>
       <c r="F18">
-        <v>55.376</v>
+        <v>58.83700000000001</v>
       </c>
       <c r="G18">
         <v>57.4</v>
@@ -2757,28 +2757,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M18">
-        <v>2.7854128</v>
+        <v>2.9595011</v>
       </c>
       <c r="N18">
-        <v>67.6145872</v>
+        <v>67.44049890000001</v>
       </c>
       <c r="O18">
-        <v>18.255938544</v>
+        <v>18.208934703</v>
       </c>
       <c r="P18">
-        <v>49.358648656</v>
+        <v>49.231564197</v>
       </c>
       <c r="Q18">
-        <v>71.75864865599999</v>
+        <v>71.631564197</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1590385043641629</v>
+        <v>0.1600794252574246</v>
       </c>
       <c r="T18">
-        <v>1.356568103498365</v>
+        <v>1.369038067579864</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.27453022402999</v>
+        <v>23.78779315202823</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1391081529636624</v>
+        <v>0.1387489222614279</v>
       </c>
       <c r="C19">
-        <v>287.130742743325</v>
+        <v>284.7850046564899</v>
       </c>
       <c r="D19">
-        <v>288.567742743325</v>
+        <v>289.6830046564899</v>
       </c>
       <c r="E19">
-        <v>-185.963</v>
+        <v>-182.502</v>
       </c>
       <c r="F19">
-        <v>58.83700000000001</v>
+        <v>62.29800000000001</v>
       </c>
       <c r="G19">
         <v>57.4</v>
@@ -2839,28 +2839,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M19">
-        <v>2.9595011</v>
+        <v>3.1335894</v>
       </c>
       <c r="N19">
-        <v>67.44049890000001</v>
+        <v>67.2664106</v>
       </c>
       <c r="O19">
-        <v>18.208934703</v>
+        <v>18.161930862</v>
       </c>
       <c r="P19">
-        <v>49.231564197</v>
+        <v>49.10447973799999</v>
       </c>
       <c r="Q19">
-        <v>71.631564197</v>
+        <v>71.50447973799999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1600794252574246</v>
+        <v>0.161145734465156</v>
       </c>
       <c r="T19">
-        <v>1.369038067579864</v>
+        <v>1.381812177126765</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.78779315202823</v>
+        <v>22.46624908802665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1387489222614279</v>
+        <v>0.1383896915591935</v>
       </c>
       <c r="C20">
-        <v>284.7850046564897</v>
+        <v>282.4479205853122</v>
       </c>
       <c r="D20">
-        <v>289.6830046564897</v>
+        <v>290.8069205853122</v>
       </c>
       <c r="E20">
-        <v>-182.502</v>
+        <v>-179.041</v>
       </c>
       <c r="F20">
-        <v>62.298</v>
+        <v>65.759</v>
       </c>
       <c r="G20">
         <v>57.4</v>
@@ -2921,28 +2921,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M20">
-        <v>3.1335894</v>
+        <v>3.3076777</v>
       </c>
       <c r="N20">
-        <v>67.2664106</v>
+        <v>67.09232230000001</v>
       </c>
       <c r="O20">
-        <v>18.161930862</v>
+        <v>18.114927021</v>
       </c>
       <c r="P20">
-        <v>49.10447973799999</v>
+        <v>48.97739527900001</v>
       </c>
       <c r="Q20">
-        <v>71.50447973799999</v>
+        <v>71.37739527900001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.161145734465156</v>
+        <v>0.1622383722953006</v>
       </c>
       <c r="T20">
-        <v>1.381812177126765</v>
+        <v>1.394901696785936</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.46624908802666</v>
+        <v>21.28381492549894</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1383896915591935</v>
+        <v>0.138030460856959</v>
       </c>
       <c r="C21">
-        <v>282.4479205853122</v>
+        <v>280.1195916500109</v>
       </c>
       <c r="D21">
-        <v>290.8069205853122</v>
+        <v>291.9395916500109</v>
       </c>
       <c r="E21">
-        <v>-179.041</v>
+        <v>-175.58</v>
       </c>
       <c r="F21">
-        <v>65.759</v>
+        <v>69.22000000000001</v>
       </c>
       <c r="G21">
         <v>57.4</v>
@@ -3003,28 +3003,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M21">
-        <v>3.3076777</v>
+        <v>3.481766</v>
       </c>
       <c r="N21">
-        <v>67.09232230000001</v>
+        <v>66.91823400000001</v>
       </c>
       <c r="O21">
-        <v>18.114927021</v>
+        <v>18.06792318</v>
       </c>
       <c r="P21">
-        <v>48.97739527900001</v>
+        <v>48.85031082</v>
       </c>
       <c r="Q21">
-        <v>71.37739527900001</v>
+        <v>71.25031082000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1622383722953006</v>
+        <v>0.1633583260711988</v>
       </c>
       <c r="T21">
-        <v>1.394901696785936</v>
+        <v>1.408318454436586</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.28381492549894</v>
+        <v>20.21962417922399</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.138030460856959</v>
+        <v>0.1376712301547246</v>
       </c>
       <c r="C22">
-        <v>280.1195916500109</v>
+        <v>277.8001205523871</v>
       </c>
       <c r="D22">
-        <v>291.9395916500109</v>
+        <v>293.0811205523871</v>
       </c>
       <c r="E22">
-        <v>-175.58</v>
+        <v>-172.119</v>
       </c>
       <c r="F22">
-        <v>69.22000000000001</v>
+        <v>72.68100000000001</v>
       </c>
       <c r="G22">
         <v>57.4</v>
@@ -3085,28 +3085,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M22">
-        <v>3.481766</v>
+        <v>3.655854300000001</v>
       </c>
       <c r="N22">
-        <v>66.91823400000001</v>
+        <v>66.7441457</v>
       </c>
       <c r="O22">
-        <v>18.06792318</v>
+        <v>18.020919339</v>
       </c>
       <c r="P22">
-        <v>48.85031082</v>
+        <v>48.723226361</v>
       </c>
       <c r="Q22">
-        <v>71.25031082000001</v>
+        <v>71.12322636100001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1633583260711988</v>
+        <v>0.1645066331072463</v>
       </c>
       <c r="T22">
-        <v>1.408318454436586</v>
+        <v>1.422074876837885</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.21962417922399</v>
+        <v>19.25678493259428</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1376712301547246</v>
+        <v>0.1373119994524901</v>
       </c>
       <c r="C23">
-        <v>277.8001205523871</v>
+        <v>275.4896116068674</v>
       </c>
       <c r="D23">
-        <v>293.0811205523871</v>
+        <v>294.2316116068674</v>
       </c>
       <c r="E23">
-        <v>-172.119</v>
+        <v>-168.658</v>
       </c>
       <c r="F23">
-        <v>72.681</v>
+        <v>76.14200000000001</v>
       </c>
       <c r="G23">
         <v>57.4</v>
@@ -3167,28 +3167,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M23">
-        <v>3.6558543</v>
+        <v>3.8299426</v>
       </c>
       <c r="N23">
-        <v>66.7441457</v>
+        <v>66.57005740000001</v>
       </c>
       <c r="O23">
-        <v>18.020919339</v>
+        <v>17.973915498</v>
       </c>
       <c r="P23">
-        <v>48.723226361</v>
+        <v>48.59614190200001</v>
       </c>
       <c r="Q23">
-        <v>71.12322636100001</v>
+        <v>70.99614190200001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1645066331072463</v>
+        <v>0.1656843839134489</v>
       </c>
       <c r="T23">
-        <v>1.422074876837885</v>
+        <v>1.436184028018705</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.25678493259428</v>
+        <v>18.38147652656727</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1373119994524901</v>
+        <v>0.1369527687502557</v>
       </c>
       <c r="C24">
-        <v>275.4896116068674</v>
+        <v>273.18817077228</v>
       </c>
       <c r="D24">
-        <v>294.2316116068674</v>
+        <v>295.3911707722801</v>
       </c>
       <c r="E24">
-        <v>-168.658</v>
+        <v>-165.197</v>
       </c>
       <c r="F24">
-        <v>76.14200000000001</v>
+        <v>79.60300000000001</v>
       </c>
       <c r="G24">
         <v>57.4</v>
@@ -3249,28 +3249,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M24">
-        <v>3.8299426</v>
+        <v>4.0040309</v>
       </c>
       <c r="N24">
-        <v>66.57005740000001</v>
+        <v>66.3959691</v>
       </c>
       <c r="O24">
-        <v>17.973915498</v>
+        <v>17.926911657</v>
       </c>
       <c r="P24">
-        <v>48.59614190200001</v>
+        <v>48.469057443</v>
       </c>
       <c r="Q24">
-        <v>70.99614190200001</v>
+        <v>70.869057443</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1656843839134489</v>
+        <v>0.1668927256496827</v>
       </c>
       <c r="T24">
-        <v>1.436184028018705</v>
+        <v>1.450659650658767</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.38147652656727</v>
+        <v>17.58228189497738</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1369527687502557</v>
+        <v>0.1365935380480212</v>
       </c>
       <c r="C25">
-        <v>273.18817077228</v>
+        <v>270.8959056843865</v>
       </c>
       <c r="D25">
-        <v>295.3911707722801</v>
+        <v>296.5599056843865</v>
       </c>
       <c r="E25">
-        <v>-165.197</v>
+        <v>-161.736</v>
       </c>
       <c r="F25">
-        <v>79.60300000000001</v>
+        <v>83.06400000000001</v>
       </c>
       <c r="G25">
         <v>57.4</v>
@@ -3331,28 +3331,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M25">
-        <v>4.0040309</v>
+        <v>4.1781192</v>
       </c>
       <c r="N25">
-        <v>66.3959691</v>
+        <v>66.22188080000001</v>
       </c>
       <c r="O25">
-        <v>17.926911657</v>
+        <v>17.879907816</v>
       </c>
       <c r="P25">
-        <v>48.469057443</v>
+        <v>48.34197298400001</v>
       </c>
       <c r="Q25">
-        <v>70.869057443</v>
+        <v>70.741972984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1668927256496827</v>
+        <v>0.1681328658526595</v>
       </c>
       <c r="T25">
-        <v>1.450659650658767</v>
+        <v>1.465516210736726</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.58228189497738</v>
+        <v>16.84968681601999</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1365935380480212</v>
+        <v>0.1362343073457868</v>
       </c>
       <c r="C26">
-        <v>270.8959056843865</v>
+        <v>268.6129256891867</v>
       </c>
       <c r="D26">
-        <v>296.5599056843865</v>
+        <v>297.7379256891867</v>
       </c>
       <c r="E26">
-        <v>-161.736</v>
+        <v>-158.275</v>
       </c>
       <c r="F26">
-        <v>83.06400000000001</v>
+        <v>86.52500000000001</v>
       </c>
       <c r="G26">
         <v>57.4</v>
@@ -3413,28 +3413,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M26">
-        <v>4.1781192</v>
+        <v>4.3522075</v>
       </c>
       <c r="N26">
-        <v>66.22188080000001</v>
+        <v>66.0477925</v>
       </c>
       <c r="O26">
-        <v>17.879907816</v>
+        <v>17.832903975</v>
       </c>
       <c r="P26">
-        <v>48.34197298400001</v>
+        <v>48.214888525</v>
       </c>
       <c r="Q26">
-        <v>70.741972984</v>
+        <v>70.614888525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1681328658526595</v>
+        <v>0.169406076461049</v>
       </c>
       <c r="T26">
-        <v>1.465516210736726</v>
+        <v>1.480768945750096</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.84968681601999</v>
+        <v>16.17569934337919</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1362343073457868</v>
+        <v>0.1358750766435523</v>
       </c>
       <c r="C27">
-        <v>268.6129256891867</v>
+        <v>266.3393418770232</v>
       </c>
       <c r="D27">
-        <v>297.7379256891867</v>
+        <v>298.9253418770232</v>
       </c>
       <c r="E27">
-        <v>-158.275</v>
+        <v>-154.814</v>
       </c>
       <c r="F27">
-        <v>86.52500000000001</v>
+        <v>89.986</v>
       </c>
       <c r="G27">
         <v>57.4</v>
@@ -3495,28 +3495,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M27">
-        <v>4.3522075</v>
+        <v>4.5262958</v>
       </c>
       <c r="N27">
-        <v>66.0477925</v>
+        <v>65.87370420000001</v>
       </c>
       <c r="O27">
-        <v>17.832903975</v>
+        <v>17.785900134</v>
       </c>
       <c r="P27">
-        <v>48.214888525</v>
+        <v>48.087804066</v>
       </c>
       <c r="Q27">
-        <v>70.614888525</v>
+        <v>70.487804066</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.169406076461049</v>
+        <v>0.1707136981669626</v>
       </c>
       <c r="T27">
-        <v>1.480768945750096</v>
+        <v>1.496433916844909</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.17569934337919</v>
+        <v>15.55355706094153</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1358750766435523</v>
+        <v>0.1355158459413179</v>
       </c>
       <c r="C28">
-        <v>266.3393418770232</v>
+        <v>264.0752671175027</v>
       </c>
       <c r="D28">
-        <v>298.9253418770232</v>
+        <v>300.1222671175028</v>
       </c>
       <c r="E28">
-        <v>-154.814</v>
+        <v>-151.353</v>
       </c>
       <c r="F28">
-        <v>89.986</v>
+        <v>93.44700000000002</v>
       </c>
       <c r="G28">
         <v>57.4</v>
@@ -3577,28 +3577,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M28">
-        <v>4.5262958</v>
+        <v>4.700384100000001</v>
       </c>
       <c r="N28">
-        <v>65.87370420000001</v>
+        <v>65.6996159</v>
       </c>
       <c r="O28">
-        <v>17.785900134</v>
+        <v>17.738896293</v>
       </c>
       <c r="P28">
-        <v>48.087804066</v>
+        <v>47.960719607</v>
       </c>
       <c r="Q28">
-        <v>70.487804066</v>
+        <v>70.36071960699999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1707136981669626</v>
+        <v>0.172057145125093</v>
       </c>
       <c r="T28">
-        <v>1.496433916844909</v>
+        <v>1.512528065229991</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.55355706094153</v>
+        <v>14.97749939201777</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1355158459413179</v>
+        <v>0.1351566152390834</v>
       </c>
       <c r="C29">
-        <v>264.0752671175027</v>
+        <v>261.8208160952628</v>
       </c>
       <c r="D29">
-        <v>300.1222671175028</v>
+        <v>301.3288160952629</v>
       </c>
       <c r="E29">
-        <v>-151.353</v>
+        <v>-147.892</v>
       </c>
       <c r="F29">
-        <v>93.44700000000002</v>
+        <v>96.90800000000002</v>
       </c>
       <c r="G29">
         <v>57.4</v>
@@ -3659,28 +3659,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M29">
-        <v>4.700384100000001</v>
+        <v>4.8744724</v>
       </c>
       <c r="N29">
-        <v>65.6996159</v>
+        <v>65.5255276</v>
       </c>
       <c r="O29">
-        <v>17.738896293</v>
+        <v>17.691892452</v>
       </c>
       <c r="P29">
-        <v>47.960719607</v>
+        <v>47.833635148</v>
       </c>
       <c r="Q29">
-        <v>70.36071960699999</v>
+        <v>70.23363514799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.172057145125093</v>
+        <v>0.1734379100542825</v>
       </c>
       <c r="T29">
-        <v>1.512528065229991</v>
+        <v>1.529069273292436</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.97749939201777</v>
+        <v>14.44258869944571</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1351566152390834</v>
+        <v>0.134797384536849</v>
       </c>
       <c r="C30">
-        <v>261.8208160952628</v>
+        <v>259.576105346601</v>
       </c>
       <c r="D30">
-        <v>301.3288160952629</v>
+        <v>302.5451053466011</v>
       </c>
       <c r="E30">
-        <v>-147.892</v>
+        <v>-144.431</v>
       </c>
       <c r="F30">
-        <v>96.90800000000002</v>
+        <v>100.369</v>
       </c>
       <c r="G30">
         <v>57.4</v>
@@ -3741,28 +3741,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M30">
-        <v>4.8744724</v>
+        <v>5.0485607</v>
       </c>
       <c r="N30">
-        <v>65.5255276</v>
+        <v>65.35143930000001</v>
       </c>
       <c r="O30">
-        <v>17.691892452</v>
+        <v>17.644888611</v>
       </c>
       <c r="P30">
-        <v>47.833635148</v>
+        <v>47.70655068900001</v>
       </c>
       <c r="Q30">
-        <v>70.23363514799999</v>
+        <v>70.10655068900002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1734379100542825</v>
+        <v>0.1748575697702098</v>
       </c>
       <c r="T30">
-        <v>1.529069273292436</v>
+        <v>1.546076430877767</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.44258869944571</v>
+        <v>13.94456839946482</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.134797384536849</v>
+        <v>0.1344381538346145</v>
       </c>
       <c r="C31">
-        <v>259.576105346601</v>
+        <v>257.3412532969976</v>
       </c>
       <c r="D31">
-        <v>302.5451053466011</v>
+        <v>303.7712532969977</v>
       </c>
       <c r="E31">
-        <v>-144.431</v>
+        <v>-140.97</v>
       </c>
       <c r="F31">
-        <v>100.369</v>
+        <v>103.83</v>
       </c>
       <c r="G31">
         <v>57.4</v>
@@ -3823,28 +3823,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M31">
-        <v>5.048560699999999</v>
+        <v>5.222649</v>
       </c>
       <c r="N31">
-        <v>65.35143930000001</v>
+        <v>65.177351</v>
       </c>
       <c r="O31">
-        <v>17.644888611</v>
+        <v>17.59788477</v>
       </c>
       <c r="P31">
-        <v>47.70655068900001</v>
+        <v>47.57946623</v>
       </c>
       <c r="Q31">
-        <v>70.10655068900002</v>
+        <v>69.97946623</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1748575697702098</v>
+        <v>0.1763177911923065</v>
       </c>
       <c r="T31">
-        <v>1.546076430877767</v>
+        <v>1.563569507251251</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.94456839946482</v>
+        <v>13.479749452816</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1344381538346145</v>
+        <v>0.1340789231323801</v>
       </c>
       <c r="C32">
-        <v>257.3412532969976</v>
+        <v>255.1163802995539</v>
       </c>
       <c r="D32">
-        <v>303.7712532969977</v>
+        <v>305.0073802995539</v>
       </c>
       <c r="E32">
-        <v>-140.97</v>
+        <v>-137.509</v>
       </c>
       <c r="F32">
-        <v>103.83</v>
+        <v>107.291</v>
       </c>
       <c r="G32">
         <v>57.4</v>
@@ -3905,28 +3905,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M32">
-        <v>5.222649</v>
+        <v>5.3967373</v>
       </c>
       <c r="N32">
-        <v>65.177351</v>
+        <v>65.00326270000001</v>
       </c>
       <c r="O32">
-        <v>17.59788477</v>
+        <v>17.550880929</v>
       </c>
       <c r="P32">
-        <v>47.57946623</v>
+        <v>47.45238177100001</v>
       </c>
       <c r="Q32">
-        <v>69.97946623</v>
+        <v>69.85238177100001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1763177911923065</v>
+        <v>0.1778203378730146</v>
       </c>
       <c r="T32">
-        <v>1.563569507251251</v>
+        <v>1.581569629316719</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.479749452816</v>
+        <v>13.0449188253058</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1340789231323801</v>
+        <v>0.1340700924301456</v>
       </c>
       <c r="C33">
-        <v>255.1163802995539</v>
+        <v>251.6858937983006</v>
       </c>
       <c r="D33">
-        <v>305.0073802995539</v>
+        <v>305.0378937983006</v>
       </c>
       <c r="E33">
-        <v>-137.509</v>
+        <v>-134.048</v>
       </c>
       <c r="F33">
-        <v>107.291</v>
+        <v>110.752</v>
       </c>
       <c r="G33">
         <v>57.4</v>
@@ -3987,45 +3987,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M33">
-        <v>5.3967373</v>
+        <v>5.736953600000001</v>
       </c>
       <c r="N33">
-        <v>65.00326270000001</v>
+        <v>64.6630464</v>
       </c>
       <c r="O33">
-        <v>17.550880929</v>
+        <v>17.459022528</v>
       </c>
       <c r="P33">
-        <v>47.45238177100001</v>
+        <v>47.20402387199999</v>
       </c>
       <c r="Q33">
-        <v>69.85238177100001</v>
+        <v>69.604023872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1778203378730146</v>
+        <v>0.1793670771031553</v>
       </c>
       <c r="T33">
-        <v>1.581569629316719</v>
+        <v>1.600099166737054</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>13.0449188253058</v>
+        <v>12.27132114158985</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1340700924301456</v>
+        <v>0.1337218117279112</v>
       </c>
       <c r="C34">
-        <v>251.6858937983006</v>
+        <v>249.4332266314428</v>
       </c>
       <c r="D34">
-        <v>305.0378937983006</v>
+        <v>306.2462266314429</v>
       </c>
       <c r="E34">
-        <v>-134.048</v>
+        <v>-130.587</v>
       </c>
       <c r="F34">
-        <v>110.752</v>
+        <v>114.213</v>
       </c>
       <c r="G34">
         <v>57.4</v>
@@ -4069,28 +4069,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M34">
-        <v>5.736953600000001</v>
+        <v>5.9162334</v>
       </c>
       <c r="N34">
-        <v>64.6630464</v>
+        <v>64.48376660000001</v>
       </c>
       <c r="O34">
-        <v>17.459022528</v>
+        <v>17.410616982</v>
       </c>
       <c r="P34">
-        <v>47.20402387199999</v>
+        <v>47.073149618</v>
       </c>
       <c r="Q34">
-        <v>69.604023872</v>
+        <v>69.47314961800001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1793670771031553</v>
+        <v>0.1809599876535988</v>
       </c>
       <c r="T34">
-        <v>1.600099166737054</v>
+        <v>1.619181824677399</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.27132114158985</v>
+        <v>11.89946292517804</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1337218117279112</v>
+        <v>0.1333735310256767</v>
       </c>
       <c r="C35">
-        <v>249.4332266314428</v>
+        <v>247.1901705651707</v>
       </c>
       <c r="D35">
-        <v>306.2462266314429</v>
+        <v>307.4641705651708</v>
       </c>
       <c r="E35">
-        <v>-130.587</v>
+        <v>-127.126</v>
       </c>
       <c r="F35">
-        <v>114.213</v>
+        <v>117.674</v>
       </c>
       <c r="G35">
         <v>57.4</v>
@@ -4151,28 +4151,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M35">
-        <v>5.9162334</v>
+        <v>6.095513200000001</v>
       </c>
       <c r="N35">
-        <v>64.48376660000001</v>
+        <v>64.30448680000001</v>
       </c>
       <c r="O35">
-        <v>17.410616982</v>
+        <v>17.362211436</v>
       </c>
       <c r="P35">
-        <v>47.073149618</v>
+        <v>46.942275364</v>
       </c>
       <c r="Q35">
-        <v>69.47314961800001</v>
+        <v>69.342275364</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1809599876535988</v>
+        <v>0.1826011682207223</v>
       </c>
       <c r="T35">
-        <v>1.619181824677399</v>
+        <v>1.638842744979573</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.89946292517804</v>
+        <v>11.54947872149633</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1333735310256767</v>
+        <v>0.1330252503234423</v>
       </c>
       <c r="C36">
-        <v>247.1901705651707</v>
+        <v>244.9568407276442</v>
       </c>
       <c r="D36">
-        <v>307.4641705651708</v>
+        <v>308.6918407276442</v>
       </c>
       <c r="E36">
-        <v>-127.126</v>
+        <v>-123.665</v>
       </c>
       <c r="F36">
-        <v>117.674</v>
+        <v>121.135</v>
       </c>
       <c r="G36">
         <v>57.4</v>
@@ -4233,28 +4233,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M36">
-        <v>6.095513200000001</v>
+        <v>6.274793000000001</v>
       </c>
       <c r="N36">
-        <v>64.30448680000001</v>
+        <v>64.125207</v>
       </c>
       <c r="O36">
-        <v>17.362211436</v>
+        <v>17.31380589</v>
       </c>
       <c r="P36">
-        <v>46.942275364</v>
+        <v>46.81140111000001</v>
       </c>
       <c r="Q36">
-        <v>69.342275364</v>
+        <v>69.21140111</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1826011682207223</v>
+        <v>0.1842928466514497</v>
       </c>
       <c r="T36">
-        <v>1.638842744979573</v>
+        <v>1.659108616675659</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.54947872149633</v>
+        <v>11.21949361516786</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1330252503234423</v>
+        <v>0.1326769696212078</v>
       </c>
       <c r="C37">
-        <v>244.9568407276442</v>
+        <v>242.7333540931705</v>
       </c>
       <c r="D37">
-        <v>308.6918407276442</v>
+        <v>309.9293540931706</v>
       </c>
       <c r="E37">
-        <v>-123.665</v>
+        <v>-120.204</v>
       </c>
       <c r="F37">
-        <v>121.135</v>
+        <v>124.596</v>
       </c>
       <c r="G37">
         <v>57.4</v>
@@ -4315,28 +4315,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M37">
-        <v>6.274793000000001</v>
+        <v>6.4540728</v>
       </c>
       <c r="N37">
-        <v>64.125207</v>
+        <v>63.94592720000001</v>
       </c>
       <c r="O37">
-        <v>17.31380589</v>
+        <v>17.265400344</v>
       </c>
       <c r="P37">
-        <v>46.81140111000001</v>
+        <v>46.680526856</v>
       </c>
       <c r="Q37">
-        <v>69.21140111</v>
+        <v>69.08052685600001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1842928466514497</v>
+        <v>0.1860373900331372</v>
       </c>
       <c r="T37">
-        <v>1.659108616675659</v>
+        <v>1.680007796862249</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.21949361516786</v>
+        <v>10.90784101474653</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1326769696212078</v>
+        <v>0.1323286889189734</v>
       </c>
       <c r="C38">
-        <v>242.7333540931704</v>
+        <v>240.5198295193579</v>
       </c>
       <c r="D38">
-        <v>309.9293540931704</v>
+        <v>311.176829519358</v>
       </c>
       <c r="E38">
-        <v>-120.204</v>
+        <v>-116.743</v>
       </c>
       <c r="F38">
-        <v>124.596</v>
+        <v>128.057</v>
       </c>
       <c r="G38">
         <v>57.4</v>
@@ -4397,28 +4397,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M38">
-        <v>6.4540728</v>
+        <v>6.6333526</v>
       </c>
       <c r="N38">
-        <v>63.94592720000001</v>
+        <v>63.7666474</v>
       </c>
       <c r="O38">
-        <v>17.265400344</v>
+        <v>17.216994798</v>
       </c>
       <c r="P38">
-        <v>46.680526856</v>
+        <v>46.549652602</v>
       </c>
       <c r="Q38">
-        <v>69.08052685600001</v>
+        <v>68.949652602</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1860373900331372</v>
+        <v>0.1878373157444022</v>
       </c>
       <c r="T38">
-        <v>1.680007796862249</v>
+        <v>1.701570443086508</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.90784101474654</v>
+        <v>10.61303450083446</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1323286889189734</v>
+        <v>0.1319804082167389</v>
       </c>
       <c r="C39">
-        <v>240.5198295193579</v>
+        <v>238.3163877851709</v>
       </c>
       <c r="D39">
-        <v>311.176829519358</v>
+        <v>312.4343877851709</v>
       </c>
       <c r="E39">
-        <v>-116.743</v>
+        <v>-113.282</v>
       </c>
       <c r="F39">
-        <v>128.057</v>
+        <v>131.518</v>
       </c>
       <c r="G39">
         <v>57.4</v>
@@ -4479,28 +4479,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M39">
-        <v>6.6333526</v>
+        <v>6.8126324</v>
       </c>
       <c r="N39">
-        <v>63.7666474</v>
+        <v>63.58736760000001</v>
       </c>
       <c r="O39">
-        <v>17.216994798</v>
+        <v>17.168589252</v>
       </c>
       <c r="P39">
-        <v>46.549652602</v>
+        <v>46.418778348</v>
       </c>
       <c r="Q39">
-        <v>68.949652602</v>
+        <v>68.818778348</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1878373157444022</v>
+        <v>0.1896953035753854</v>
       </c>
       <c r="T39">
-        <v>1.701570443086508</v>
+        <v>1.723828658543807</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.61303450083446</v>
+        <v>10.33374411923356</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1319804082167389</v>
+        <v>0.1316321275145045</v>
       </c>
       <c r="C40">
-        <v>238.3163877851709</v>
+        <v>236.1231516299109</v>
       </c>
       <c r="D40">
-        <v>312.4343877851709</v>
+        <v>313.7021516299109</v>
       </c>
       <c r="E40">
-        <v>-113.282</v>
+        <v>-109.821</v>
       </c>
       <c r="F40">
-        <v>131.518</v>
+        <v>134.979</v>
       </c>
       <c r="G40">
         <v>57.4</v>
@@ -4561,28 +4561,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M40">
-        <v>6.8126324</v>
+        <v>6.991912200000001</v>
       </c>
       <c r="N40">
-        <v>63.58736760000001</v>
+        <v>63.4080878</v>
       </c>
       <c r="O40">
-        <v>17.168589252</v>
+        <v>17.120183706</v>
       </c>
       <c r="P40">
-        <v>46.418778348</v>
+        <v>46.287904094</v>
       </c>
       <c r="Q40">
-        <v>68.818778348</v>
+        <v>68.687904094</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1896953035753854</v>
+        <v>0.1916142090401713</v>
       </c>
       <c r="T40">
-        <v>1.723828658543807</v>
+        <v>1.746816651557084</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.33374411923356</v>
+        <v>10.06877632130449</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1316321275145045</v>
+        <v>0.13128384681227</v>
       </c>
       <c r="C41">
-        <v>236.1231516299109</v>
+        <v>233.9402457931516</v>
       </c>
       <c r="D41">
-        <v>313.7021516299109</v>
+        <v>314.9802457931517</v>
       </c>
       <c r="E41">
-        <v>-109.821</v>
+        <v>-106.36</v>
       </c>
       <c r="F41">
-        <v>134.979</v>
+        <v>138.44</v>
       </c>
       <c r="G41">
         <v>57.4</v>
@@ -4643,28 +4643,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M41">
-        <v>6.991912200000001</v>
+        <v>7.171192000000001</v>
       </c>
       <c r="N41">
-        <v>63.4080878</v>
+        <v>63.228808</v>
       </c>
       <c r="O41">
-        <v>17.120183706</v>
+        <v>17.07177816</v>
       </c>
       <c r="P41">
-        <v>46.287904094</v>
+        <v>46.15702984</v>
       </c>
       <c r="Q41">
-        <v>68.687904094</v>
+        <v>68.55702984</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1916142090401713</v>
+        <v>0.1935970780204501</v>
       </c>
       <c r="T41">
-        <v>1.746816651557084</v>
+        <v>1.770570911004137</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.06877632130449</v>
+        <v>9.817056913271879</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.13128384681227</v>
+        <v>0.1314443761100356</v>
       </c>
       <c r="C42">
-        <v>233.9402457931516</v>
+        <v>229.888856091413</v>
       </c>
       <c r="D42">
-        <v>314.9802457931517</v>
+        <v>314.389856091413</v>
       </c>
       <c r="E42">
-        <v>-106.36</v>
+        <v>-102.899</v>
       </c>
       <c r="F42">
-        <v>138.44</v>
+        <v>141.901</v>
       </c>
       <c r="G42">
         <v>57.4</v>
@@ -4725,45 +4725,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M42">
-        <v>7.171192000000001</v>
+        <v>7.5917035</v>
       </c>
       <c r="N42">
-        <v>63.228808</v>
+        <v>62.8082965</v>
       </c>
       <c r="O42">
-        <v>17.07177816</v>
+        <v>16.958240055</v>
       </c>
       <c r="P42">
-        <v>46.15702984</v>
+        <v>45.85005644500001</v>
       </c>
       <c r="Q42">
-        <v>68.55702984</v>
+        <v>68.25005644500001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1935970780204501</v>
+        <v>0.1956471628983654</v>
       </c>
       <c r="T42">
-        <v>1.770570911004137</v>
+        <v>1.795130399584987</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>9.817056913271879</v>
+        <v>9.273281023159031</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1314443761100356</v>
+        <v>0.1311085054078011</v>
       </c>
       <c r="C43">
-        <v>229.888856091413</v>
+        <v>227.6656499225911</v>
       </c>
       <c r="D43">
-        <v>314.389856091413</v>
+        <v>315.6276499225912</v>
       </c>
       <c r="E43">
-        <v>-102.899</v>
+        <v>-99.43799999999999</v>
       </c>
       <c r="F43">
-        <v>141.901</v>
+        <v>145.362</v>
       </c>
       <c r="G43">
         <v>57.4</v>
@@ -4807,28 +4807,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M43">
-        <v>7.5917035</v>
+        <v>7.776867000000001</v>
       </c>
       <c r="N43">
-        <v>62.8082965</v>
+        <v>62.623133</v>
       </c>
       <c r="O43">
-        <v>16.958240055</v>
+        <v>16.90824591</v>
       </c>
       <c r="P43">
-        <v>45.85005644500001</v>
+        <v>45.71488709</v>
       </c>
       <c r="Q43">
-        <v>68.25005644500001</v>
+        <v>68.11488709</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1956471628983654</v>
+        <v>0.1977679403582778</v>
       </c>
       <c r="T43">
-        <v>1.795130399584987</v>
+        <v>1.82053676708242</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.273281023159031</v>
+        <v>9.05248861784572</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1311085054078011</v>
+        <v>0.1307726347055667</v>
       </c>
       <c r="C44">
-        <v>227.6656499225913</v>
+        <v>225.4522289907399</v>
       </c>
       <c r="D44">
-        <v>315.6276499225913</v>
+        <v>316.8752289907399</v>
       </c>
       <c r="E44">
-        <v>-99.43800000000002</v>
+        <v>-95.977</v>
       </c>
       <c r="F44">
-        <v>145.362</v>
+        <v>148.823</v>
       </c>
       <c r="G44">
         <v>57.4</v>
@@ -4889,28 +4889,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M44">
-        <v>7.776866999999999</v>
+        <v>7.9620305</v>
       </c>
       <c r="N44">
-        <v>62.62313300000001</v>
+        <v>62.43796950000001</v>
       </c>
       <c r="O44">
-        <v>16.90824591000001</v>
+        <v>16.858251765</v>
       </c>
       <c r="P44">
-        <v>45.71488709</v>
+        <v>45.579717735</v>
       </c>
       <c r="Q44">
-        <v>68.11488709</v>
+        <v>67.97971773500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1977679403582778</v>
+        <v>0.1999631310623977</v>
       </c>
       <c r="T44">
-        <v>1.820536767082419</v>
+        <v>1.846834586070989</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.052488617845723</v>
+        <v>8.841965626733032</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1307726347055667</v>
+        <v>0.1304367640033322</v>
       </c>
       <c r="C45">
-        <v>225.4522289907399</v>
+        <v>223.2487097904267</v>
       </c>
       <c r="D45">
-        <v>316.8752289907399</v>
+        <v>318.1327097904268</v>
       </c>
       <c r="E45">
-        <v>-95.977</v>
+        <v>-92.51599999999999</v>
       </c>
       <c r="F45">
-        <v>148.823</v>
+        <v>152.284</v>
       </c>
       <c r="G45">
         <v>57.4</v>
@@ -4971,28 +4971,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M45">
-        <v>7.9620305</v>
+        <v>8.147194000000001</v>
       </c>
       <c r="N45">
-        <v>62.43796950000001</v>
+        <v>62.25280600000001</v>
       </c>
       <c r="O45">
-        <v>16.858251765</v>
+        <v>16.80825762</v>
       </c>
       <c r="P45">
-        <v>45.579717735</v>
+        <v>45.44454838</v>
       </c>
       <c r="Q45">
-        <v>67.97971773500001</v>
+        <v>67.84454837999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1999631310623977</v>
+        <v>0.2022367214345218</v>
       </c>
       <c r="T45">
-        <v>1.846834586070989</v>
+        <v>1.874071612880579</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.841965626733032</v>
+        <v>8.641011862489098</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1304367640033322</v>
+        <v>0.1301008933010978</v>
       </c>
       <c r="C46">
-        <v>223.2487097904267</v>
+        <v>221.0552106727652</v>
       </c>
       <c r="D46">
-        <v>318.1327097904268</v>
+        <v>319.4002106727652</v>
       </c>
       <c r="E46">
-        <v>-92.51599999999999</v>
+        <v>-89.05500000000001</v>
       </c>
       <c r="F46">
-        <v>152.284</v>
+        <v>155.745</v>
       </c>
       <c r="G46">
         <v>57.4</v>
@@ -5053,28 +5053,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M46">
-        <v>8.147194000000001</v>
+        <v>8.332357500000001</v>
       </c>
       <c r="N46">
-        <v>62.25280600000001</v>
+        <v>62.06764250000001</v>
       </c>
       <c r="O46">
-        <v>16.80825762</v>
+        <v>16.758263475</v>
       </c>
       <c r="P46">
-        <v>45.44454838</v>
+        <v>45.309379025</v>
       </c>
       <c r="Q46">
-        <v>67.84454837999999</v>
+        <v>67.709379025</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2022367214345218</v>
+        <v>0.2045929878201778</v>
       </c>
       <c r="T46">
-        <v>1.874071612880579</v>
+        <v>1.9022990770287</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.641011862489098</v>
+        <v>8.448989376656007</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1301008933010978</v>
+        <v>0.1297650225988633</v>
       </c>
       <c r="C47">
-        <v>221.0552106727652</v>
+        <v>218.8718518825461</v>
       </c>
       <c r="D47">
-        <v>319.4002106727652</v>
+        <v>320.6778518825462</v>
       </c>
       <c r="E47">
-        <v>-89.05500000000001</v>
+        <v>-85.59399999999999</v>
       </c>
       <c r="F47">
-        <v>155.745</v>
+        <v>159.206</v>
       </c>
       <c r="G47">
         <v>57.4</v>
@@ -5135,28 +5135,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M47">
-        <v>8.332357500000001</v>
+        <v>8.517521</v>
       </c>
       <c r="N47">
-        <v>62.06764250000001</v>
+        <v>61.882479</v>
       </c>
       <c r="O47">
-        <v>16.758263475</v>
+        <v>16.70826933</v>
       </c>
       <c r="P47">
-        <v>45.309379025</v>
+        <v>45.17420967</v>
       </c>
       <c r="Q47">
-        <v>67.709379025</v>
+        <v>67.57420966999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2045929878201778</v>
+        <v>0.2070365233312284</v>
       </c>
       <c r="T47">
-        <v>1.9022990770287</v>
+        <v>1.931572002811937</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.448989376656007</v>
+        <v>8.26531569455479</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1297650225988633</v>
+        <v>0.1294291518966289</v>
       </c>
       <c r="C48">
-        <v>218.8718518825461</v>
+        <v>216.698755596265</v>
       </c>
       <c r="D48">
-        <v>320.6778518825462</v>
+        <v>321.9657555962651</v>
       </c>
       <c r="E48">
-        <v>-85.59399999999999</v>
+        <v>-82.13299999999998</v>
       </c>
       <c r="F48">
-        <v>159.206</v>
+        <v>162.667</v>
       </c>
       <c r="G48">
         <v>57.4</v>
@@ -5217,28 +5217,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M48">
-        <v>8.517521</v>
+        <v>8.702684500000002</v>
       </c>
       <c r="N48">
-        <v>61.882479</v>
+        <v>61.6973155</v>
       </c>
       <c r="O48">
-        <v>16.70826933</v>
+        <v>16.658275185</v>
       </c>
       <c r="P48">
-        <v>45.17420967</v>
+        <v>45.039040315</v>
       </c>
       <c r="Q48">
-        <v>67.57420966999999</v>
+        <v>67.439040315</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2070365233312284</v>
+        <v>0.2095722677294884</v>
       </c>
       <c r="T48">
-        <v>1.931572002811937</v>
+        <v>1.961949567303974</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.26531569455479</v>
+        <v>8.089457913819579</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1294291518966289</v>
+        <v>0.1290932811943944</v>
       </c>
       <c r="C49">
-        <v>216.698755596265</v>
+        <v>214.5360459610687</v>
       </c>
       <c r="D49">
-        <v>321.9657555962651</v>
+        <v>323.2640459610687</v>
       </c>
       <c r="E49">
-        <v>-82.13299999999998</v>
+        <v>-78.672</v>
       </c>
       <c r="F49">
-        <v>162.667</v>
+        <v>166.128</v>
       </c>
       <c r="G49">
         <v>57.4</v>
@@ -5299,28 +5299,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M49">
-        <v>8.702684500000002</v>
+        <v>8.887848</v>
       </c>
       <c r="N49">
-        <v>61.6973155</v>
+        <v>61.51215200000001</v>
       </c>
       <c r="O49">
-        <v>16.658275185</v>
+        <v>16.60828104</v>
       </c>
       <c r="P49">
-        <v>45.039040315</v>
+        <v>44.90387096000001</v>
       </c>
       <c r="Q49">
-        <v>67.439040315</v>
+        <v>67.30387096000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2095722677294884</v>
+        <v>0.2122055407584508</v>
       </c>
       <c r="T49">
-        <v>1.961949567303974</v>
+        <v>1.99349549966109</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.089457913819579</v>
+        <v>7.920927540615007</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1290932811943944</v>
+        <v>0.12875741049216</v>
       </c>
       <c r="C50">
-        <v>214.5360459610687</v>
+        <v>212.3838491346484</v>
       </c>
       <c r="D50">
-        <v>323.2640459610687</v>
+        <v>324.5728491346484</v>
       </c>
       <c r="E50">
-        <v>-78.672</v>
+        <v>-75.21100000000001</v>
       </c>
       <c r="F50">
-        <v>166.128</v>
+        <v>169.589</v>
       </c>
       <c r="G50">
         <v>57.4</v>
@@ -5381,28 +5381,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M50">
-        <v>8.887848</v>
+        <v>9.0730115</v>
       </c>
       <c r="N50">
-        <v>61.51215200000001</v>
+        <v>61.32698850000001</v>
       </c>
       <c r="O50">
-        <v>16.60828104</v>
+        <v>16.558286895</v>
       </c>
       <c r="P50">
-        <v>44.90387096000001</v>
+        <v>44.768701605</v>
       </c>
       <c r="Q50">
-        <v>67.30387096000001</v>
+        <v>67.168701605</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2122055407584508</v>
+        <v>0.2149420793963921</v>
       </c>
       <c r="T50">
-        <v>1.99349549966109</v>
+        <v>2.02627852740476</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.920927540615007</v>
+        <v>7.759275958153476</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.12875741049216</v>
+        <v>0.1287135397899255</v>
       </c>
       <c r="C51">
-        <v>212.3838491346484</v>
+        <v>209.0945851243775</v>
       </c>
       <c r="D51">
-        <v>324.5728491346484</v>
+        <v>324.7445851243775</v>
       </c>
       <c r="E51">
-        <v>-75.21100000000001</v>
+        <v>-71.75</v>
       </c>
       <c r="F51">
-        <v>169.589</v>
+        <v>173.05</v>
       </c>
       <c r="G51">
         <v>57.4</v>
@@ -5463,45 +5463,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M51">
-        <v>9.0730115</v>
+        <v>9.396615000000001</v>
       </c>
       <c r="N51">
-        <v>61.32698850000001</v>
+        <v>61.00338500000001</v>
       </c>
       <c r="O51">
-        <v>16.558286895</v>
+        <v>16.47091395</v>
       </c>
       <c r="P51">
-        <v>44.768701605</v>
+        <v>44.53247105000001</v>
       </c>
       <c r="Q51">
-        <v>67.168701605</v>
+        <v>66.93247105</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2149420793963921</v>
+        <v>0.2177880795798511</v>
       </c>
       <c r="T51">
-        <v>2.02627852740476</v>
+        <v>2.060372876258177</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.759275958153476</v>
+        <v>7.492059640625906</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1287135397899255</v>
+        <v>0.1283835090876911</v>
       </c>
       <c r="C52">
-        <v>209.0945851243775</v>
+        <v>206.9313706587948</v>
       </c>
       <c r="D52">
-        <v>324.7445851243775</v>
+        <v>326.0423706587949</v>
       </c>
       <c r="E52">
-        <v>-71.75</v>
+        <v>-68.28899999999999</v>
       </c>
       <c r="F52">
-        <v>173.05</v>
+        <v>176.511</v>
       </c>
       <c r="G52">
         <v>57.4</v>
@@ -5545,28 +5545,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M52">
-        <v>9.396615000000001</v>
+        <v>9.584547300000002</v>
       </c>
       <c r="N52">
-        <v>61.00338500000001</v>
+        <v>60.8154527</v>
       </c>
       <c r="O52">
-        <v>16.47091395</v>
+        <v>16.420172229</v>
       </c>
       <c r="P52">
-        <v>44.53247105000001</v>
+        <v>44.395280471</v>
       </c>
       <c r="Q52">
-        <v>66.93247105</v>
+        <v>66.795280471</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2177880795798511</v>
+        <v>0.2207502430361042</v>
       </c>
       <c r="T52">
-        <v>2.060372876258177</v>
+        <v>2.095858831187243</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.492059640625906</v>
+        <v>7.345156510417554</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1283835090876911</v>
+        <v>0.1280534783854566</v>
       </c>
       <c r="C53">
-        <v>206.9313706587948</v>
+        <v>204.7785705630281</v>
       </c>
       <c r="D53">
-        <v>326.0423706587949</v>
+        <v>327.3505705630282</v>
       </c>
       <c r="E53">
-        <v>-68.28899999999999</v>
+        <v>-64.828</v>
       </c>
       <c r="F53">
-        <v>176.511</v>
+        <v>179.972</v>
       </c>
       <c r="G53">
         <v>57.4</v>
@@ -5627,28 +5627,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M53">
-        <v>9.584547300000002</v>
+        <v>9.7724796</v>
       </c>
       <c r="N53">
-        <v>60.8154527</v>
+        <v>60.62752040000001</v>
       </c>
       <c r="O53">
-        <v>16.420172229</v>
+        <v>16.369430508</v>
       </c>
       <c r="P53">
-        <v>44.395280471</v>
+        <v>44.258089892</v>
       </c>
       <c r="Q53">
-        <v>66.795280471</v>
+        <v>66.65808989199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2207502430361042</v>
+        <v>0.2238358299697013</v>
       </c>
       <c r="T53">
-        <v>2.095858831187243</v>
+        <v>2.132823367571687</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.345156510417554</v>
+        <v>7.203903500601833</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1280534783854566</v>
+        <v>0.1277234476832222</v>
       </c>
       <c r="C54">
-        <v>204.7785705630281</v>
+        <v>202.6363107007419</v>
       </c>
       <c r="D54">
-        <v>327.3505705630282</v>
+        <v>328.669310700742</v>
       </c>
       <c r="E54">
-        <v>-64.828</v>
+        <v>-61.36699999999999</v>
       </c>
       <c r="F54">
-        <v>179.972</v>
+        <v>183.433</v>
       </c>
       <c r="G54">
         <v>57.4</v>
@@ -5709,28 +5709,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M54">
-        <v>9.7724796</v>
+        <v>9.960411900000002</v>
       </c>
       <c r="N54">
-        <v>60.62752040000001</v>
+        <v>60.4395881</v>
       </c>
       <c r="O54">
-        <v>16.369430508</v>
+        <v>16.318688787</v>
       </c>
       <c r="P54">
-        <v>44.258089892</v>
+        <v>44.120899313</v>
       </c>
       <c r="Q54">
-        <v>66.65808989199999</v>
+        <v>66.520899313</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2238358299697013</v>
+        <v>0.2270527184749408</v>
       </c>
       <c r="T54">
-        <v>2.132823367571687</v>
+        <v>2.171360862951214</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.203903500601833</v>
+        <v>7.067980793043307</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1277234476832222</v>
+        <v>0.1273934169809877</v>
       </c>
       <c r="C55">
-        <v>202.6363107007419</v>
+        <v>200.5047189719847</v>
       </c>
       <c r="D55">
-        <v>328.669310700742</v>
+        <v>329.9987189719847</v>
       </c>
       <c r="E55">
-        <v>-61.36699999999999</v>
+        <v>-57.90599999999998</v>
       </c>
       <c r="F55">
-        <v>183.433</v>
+        <v>186.894</v>
       </c>
       <c r="G55">
         <v>57.4</v>
@@ -5791,28 +5791,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M55">
-        <v>9.960411900000002</v>
+        <v>10.1483442</v>
       </c>
       <c r="N55">
-        <v>60.4395881</v>
+        <v>60.2516558</v>
       </c>
       <c r="O55">
-        <v>16.318688787</v>
+        <v>16.267947066</v>
       </c>
       <c r="P55">
-        <v>44.120899313</v>
+        <v>43.983708734</v>
       </c>
       <c r="Q55">
-        <v>66.520899313</v>
+        <v>66.38370873400001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2270527184749408</v>
+        <v>0.2304094716977994</v>
       </c>
       <c r="T55">
-        <v>2.171360862951214</v>
+        <v>2.211573901608111</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.067980793043307</v>
+        <v>6.937092259838801</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1273934169809877</v>
+        <v>0.1270633862787533</v>
       </c>
       <c r="C56">
-        <v>200.5047189719847</v>
+        <v>198.3839253545394</v>
       </c>
       <c r="D56">
-        <v>329.9987189719847</v>
+        <v>331.3389253545395</v>
       </c>
       <c r="E56">
-        <v>-57.90599999999998</v>
+        <v>-54.44499999999999</v>
       </c>
       <c r="F56">
-        <v>186.894</v>
+        <v>190.355</v>
       </c>
       <c r="G56">
         <v>57.4</v>
@@ -5873,28 +5873,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M56">
-        <v>10.1483442</v>
+        <v>10.3362765</v>
       </c>
       <c r="N56">
-        <v>60.2516558</v>
+        <v>60.06372350000001</v>
       </c>
       <c r="O56">
-        <v>16.267947066</v>
+        <v>16.217205345</v>
       </c>
       <c r="P56">
-        <v>43.983708734</v>
+        <v>43.84651815500001</v>
       </c>
       <c r="Q56">
-        <v>66.38370873400001</v>
+        <v>66.246518155</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2304094716977994</v>
+        <v>0.2339154139527851</v>
       </c>
       <c r="T56">
-        <v>2.211573901608111</v>
+        <v>2.253574186427537</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.937092259838801</v>
+        <v>6.810963309659916</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1270633862787533</v>
+        <v>0.1267333555765188</v>
       </c>
       <c r="C57">
-        <v>198.3839253545394</v>
+        <v>196.2740619462871</v>
       </c>
       <c r="D57">
-        <v>331.3389253545395</v>
+        <v>332.6900619462872</v>
       </c>
       <c r="E57">
-        <v>-54.44499999999999</v>
+        <v>-50.98399999999998</v>
       </c>
       <c r="F57">
-        <v>190.355</v>
+        <v>193.816</v>
       </c>
       <c r="G57">
         <v>57.4</v>
@@ -5955,28 +5955,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M57">
-        <v>10.3362765</v>
+        <v>10.5242088</v>
       </c>
       <c r="N57">
-        <v>60.06372350000001</v>
+        <v>59.8757912</v>
       </c>
       <c r="O57">
-        <v>16.217205345</v>
+        <v>16.166463624</v>
       </c>
       <c r="P57">
-        <v>43.84651815500001</v>
+        <v>43.709327576</v>
       </c>
       <c r="Q57">
-        <v>66.246518155</v>
+        <v>66.109327576</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2339154139527851</v>
+        <v>0.237580717219361</v>
       </c>
       <c r="T57">
-        <v>2.253574186427537</v>
+        <v>2.297483575102392</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.810963309659916</v>
+        <v>6.689338964844558</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1267333555765188</v>
+        <v>0.1264033248742844</v>
       </c>
       <c r="C58">
-        <v>196.2740619462871</v>
+        <v>194.1752630086106</v>
       </c>
       <c r="D58">
-        <v>332.6900619462872</v>
+        <v>334.0522630086106</v>
       </c>
       <c r="E58">
-        <v>-50.98399999999998</v>
+        <v>-47.52299999999997</v>
       </c>
       <c r="F58">
-        <v>193.816</v>
+        <v>197.277</v>
       </c>
       <c r="G58">
         <v>57.4</v>
@@ -6037,28 +6037,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M58">
-        <v>10.5242088</v>
+        <v>10.7121411</v>
       </c>
       <c r="N58">
-        <v>59.8757912</v>
+        <v>59.6878589</v>
       </c>
       <c r="O58">
-        <v>16.166463624</v>
+        <v>16.115721903</v>
       </c>
       <c r="P58">
-        <v>43.709327576</v>
+        <v>43.572136997</v>
       </c>
       <c r="Q58">
-        <v>66.109327576</v>
+        <v>65.97213699700001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.237580717219361</v>
+        <v>0.2414164997076381</v>
       </c>
       <c r="T58">
-        <v>2.297483575102392</v>
+        <v>2.343435260924914</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.689338964844558</v>
+        <v>6.571982140899917</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1264033248742844</v>
+        <v>0.1260732941720499</v>
       </c>
       <c r="C59">
-        <v>194.1752630086106</v>
+        <v>192.0876650108686</v>
       </c>
       <c r="D59">
-        <v>334.0522630086106</v>
+        <v>335.4256650108687</v>
       </c>
       <c r="E59">
-        <v>-47.52299999999997</v>
+        <v>-44.06199999999998</v>
       </c>
       <c r="F59">
-        <v>197.277</v>
+        <v>200.738</v>
       </c>
       <c r="G59">
         <v>57.4</v>
@@ -6119,28 +6119,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M59">
-        <v>10.7121411</v>
+        <v>10.9000734</v>
       </c>
       <c r="N59">
-        <v>59.6878589</v>
+        <v>59.4999266</v>
       </c>
       <c r="O59">
-        <v>16.115721903</v>
+        <v>16.064980182</v>
       </c>
       <c r="P59">
-        <v>43.572136997</v>
+        <v>43.434946418</v>
       </c>
       <c r="Q59">
-        <v>65.97213699700001</v>
+        <v>65.83494641799999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2414164997076381</v>
+        <v>0.2454349385048808</v>
       </c>
       <c r="T59">
-        <v>2.343435260924914</v>
+        <v>2.391575122262795</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.571982140899917</v>
+        <v>6.458672103987849</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1260732941720499</v>
+        <v>0.1257432634698155</v>
       </c>
       <c r="C60">
-        <v>192.0876650108688</v>
+        <v>190.0114066759722</v>
       </c>
       <c r="D60">
-        <v>335.4256650108688</v>
+        <v>336.8104066759722</v>
       </c>
       <c r="E60">
-        <v>-44.06200000000001</v>
+        <v>-40.601</v>
       </c>
       <c r="F60">
-        <v>200.738</v>
+        <v>204.199</v>
       </c>
       <c r="G60">
         <v>57.4</v>
@@ -6201,28 +6201,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M60">
-        <v>10.9000734</v>
+        <v>11.0880057</v>
       </c>
       <c r="N60">
-        <v>59.49992660000001</v>
+        <v>59.31199430000001</v>
       </c>
       <c r="O60">
-        <v>16.064980182</v>
+        <v>16.01423846100001</v>
       </c>
       <c r="P60">
-        <v>43.43494641800001</v>
+        <v>43.297755839</v>
       </c>
       <c r="Q60">
-        <v>65.83494641800002</v>
+        <v>65.697755839</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2454349385048807</v>
+        <v>0.249649398706867</v>
       </c>
       <c r="T60">
-        <v>2.391575122262794</v>
+        <v>2.442063269519595</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.458672103987851</v>
+        <v>6.349203085276192</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1257432634698155</v>
+        <v>0.125413232767581</v>
       </c>
       <c r="C61">
-        <v>190.0114066759722</v>
+        <v>187.9466290270936</v>
       </c>
       <c r="D61">
-        <v>336.8104066759722</v>
+        <v>338.2066290270936</v>
       </c>
       <c r="E61">
-        <v>-40.601</v>
+        <v>-37.14000000000001</v>
       </c>
       <c r="F61">
-        <v>204.199</v>
+        <v>207.66</v>
       </c>
       <c r="G61">
         <v>57.4</v>
@@ -6283,28 +6283,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M61">
-        <v>11.0880057</v>
+        <v>11.275938</v>
       </c>
       <c r="N61">
-        <v>59.31199430000001</v>
+        <v>59.12406200000001</v>
       </c>
       <c r="O61">
-        <v>16.01423846100001</v>
+        <v>15.96349674</v>
       </c>
       <c r="P61">
-        <v>43.297755839</v>
+        <v>43.16056526000001</v>
       </c>
       <c r="Q61">
-        <v>65.697755839</v>
+        <v>65.56056526</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.249649398706867</v>
+        <v>0.2540745819189525</v>
       </c>
       <c r="T61">
-        <v>2.442063269519595</v>
+        <v>2.495075824139237</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.349203085276192</v>
+        <v>6.243383033854923</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.125413232767581</v>
+        <v>0.1250832020653466</v>
       </c>
       <c r="C62">
-        <v>187.9466290270936</v>
+        <v>185.8934754355443</v>
       </c>
       <c r="D62">
-        <v>338.2066290270936</v>
+        <v>339.6144754355443</v>
       </c>
       <c r="E62">
-        <v>-37.14000000000001</v>
+        <v>-33.679</v>
       </c>
       <c r="F62">
-        <v>207.66</v>
+        <v>211.121</v>
       </c>
       <c r="G62">
         <v>57.4</v>
@@ -6365,28 +6365,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M62">
-        <v>11.275938</v>
+        <v>11.4638703</v>
       </c>
       <c r="N62">
-        <v>59.12406200000001</v>
+        <v>58.93612970000001</v>
       </c>
       <c r="O62">
-        <v>15.96349674</v>
+        <v>15.912755019</v>
       </c>
       <c r="P62">
-        <v>43.16056526000001</v>
+        <v>43.02337468100001</v>
       </c>
       <c r="Q62">
-        <v>65.56056526</v>
+        <v>65.42337468100001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2540745819189525</v>
+        <v>0.2587266976034527</v>
       </c>
       <c r="T62">
-        <v>2.495075824139237</v>
+        <v>2.550806971303476</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.243383033854923</v>
+        <v>6.141032492316318</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1250832020653466</v>
+        <v>0.1252057713631121</v>
       </c>
       <c r="C63">
-        <v>185.8934754355443</v>
+        <v>181.9082527367331</v>
       </c>
       <c r="D63">
-        <v>339.6144754355443</v>
+        <v>339.0902527367331</v>
       </c>
       <c r="E63">
-        <v>-33.679</v>
+        <v>-30.21799999999999</v>
       </c>
       <c r="F63">
-        <v>211.121</v>
+        <v>214.582</v>
       </c>
       <c r="G63">
         <v>57.4</v>
@@ -6447,45 +6447,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M63">
-        <v>11.4638703</v>
+        <v>11.8663846</v>
       </c>
       <c r="N63">
-        <v>58.93612970000001</v>
+        <v>58.5336154</v>
       </c>
       <c r="O63">
-        <v>15.912755019</v>
+        <v>15.804076158</v>
       </c>
       <c r="P63">
-        <v>43.02337468100001</v>
+        <v>42.729539242</v>
       </c>
       <c r="Q63">
-        <v>65.42337468100001</v>
+        <v>65.12953924199999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2587266976034527</v>
+        <v>0.263623661481874</v>
       </c>
       <c r="T63">
-        <v>2.550806971303476</v>
+        <v>2.609471336739516</v>
       </c>
       <c r="U63">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>6.141032492316318</v>
+        <v>5.932725288543234</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1252057713631121</v>
+        <v>0.1248830406608777</v>
       </c>
       <c r="C64">
-        <v>181.9082527367331</v>
+        <v>179.8310492431909</v>
       </c>
       <c r="D64">
-        <v>339.0902527367331</v>
+        <v>340.4740492431909</v>
       </c>
       <c r="E64">
-        <v>-30.21799999999999</v>
+        <v>-26.75700000000001</v>
       </c>
       <c r="F64">
-        <v>214.582</v>
+        <v>218.043</v>
       </c>
       <c r="G64">
         <v>57.4</v>
@@ -6529,28 +6529,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M64">
-        <v>11.8663846</v>
+        <v>12.0577779</v>
       </c>
       <c r="N64">
-        <v>58.5336154</v>
+        <v>58.3422221</v>
       </c>
       <c r="O64">
-        <v>15.804076158</v>
+        <v>15.752399967</v>
       </c>
       <c r="P64">
-        <v>42.729539242</v>
+        <v>42.589822133</v>
       </c>
       <c r="Q64">
-        <v>65.12953924199999</v>
+        <v>64.98982213299999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.263623661481874</v>
+        <v>0.2687853261104802</v>
       </c>
       <c r="T64">
-        <v>2.609471336739516</v>
+        <v>2.671306748955883</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.932725288543234</v>
+        <v>5.838555045867945</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1248830406608777</v>
+        <v>0.1245603099586432</v>
       </c>
       <c r="C65">
-        <v>179.8310492431909</v>
+        <v>177.7651863250861</v>
       </c>
       <c r="D65">
-        <v>340.4740492431909</v>
+        <v>341.8691863250861</v>
       </c>
       <c r="E65">
-        <v>-26.75700000000001</v>
+        <v>-23.29599999999999</v>
       </c>
       <c r="F65">
-        <v>218.043</v>
+        <v>221.504</v>
       </c>
       <c r="G65">
         <v>57.4</v>
@@ -6611,28 +6611,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M65">
-        <v>12.0577779</v>
+        <v>12.2491712</v>
       </c>
       <c r="N65">
-        <v>58.3422221</v>
+        <v>58.15082880000001</v>
       </c>
       <c r="O65">
-        <v>15.752399967</v>
+        <v>15.700723776</v>
       </c>
       <c r="P65">
-        <v>42.589822133</v>
+        <v>42.450105024</v>
       </c>
       <c r="Q65">
-        <v>64.98982213299999</v>
+        <v>64.850105024</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2687853261104802</v>
+        <v>0.2742337498851201</v>
       </c>
       <c r="T65">
-        <v>2.671306748955883</v>
+        <v>2.736577461850938</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.838555045867945</v>
+        <v>5.747327623276259</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1245603099586432</v>
+        <v>0.1242375792564088</v>
       </c>
       <c r="C66">
-        <v>177.7651863250861</v>
+        <v>175.7108039645002</v>
       </c>
       <c r="D66">
-        <v>341.8691863250861</v>
+        <v>343.2758039645003</v>
       </c>
       <c r="E66">
-        <v>-23.29599999999999</v>
+        <v>-19.83499999999998</v>
       </c>
       <c r="F66">
-        <v>221.504</v>
+        <v>224.965</v>
       </c>
       <c r="G66">
         <v>57.4</v>
@@ -6693,28 +6693,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M66">
-        <v>12.2491712</v>
+        <v>12.4405645</v>
       </c>
       <c r="N66">
-        <v>58.15082880000001</v>
+        <v>57.9594355</v>
       </c>
       <c r="O66">
-        <v>15.700723776</v>
+        <v>15.649047585</v>
       </c>
       <c r="P66">
-        <v>42.450105024</v>
+        <v>42.31038791500001</v>
       </c>
       <c r="Q66">
-        <v>64.850105024</v>
+        <v>64.71038791500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2742337498851201</v>
+        <v>0.279993512161168</v>
       </c>
       <c r="T66">
-        <v>2.736577461850938</v>
+        <v>2.805577929768566</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.747327623276259</v>
+        <v>5.658907198302778</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1242375792564088</v>
+        <v>0.1239148485541743</v>
       </c>
       <c r="C67">
-        <v>175.7108039645002</v>
+        <v>173.6680444568533</v>
       </c>
       <c r="D67">
-        <v>343.2758039645003</v>
+        <v>344.6940444568534</v>
       </c>
       <c r="E67">
-        <v>-19.83499999999998</v>
+        <v>-16.374</v>
       </c>
       <c r="F67">
-        <v>224.965</v>
+        <v>228.426</v>
       </c>
       <c r="G67">
         <v>57.4</v>
@@ -6775,28 +6775,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M67">
-        <v>12.4405645</v>
+        <v>12.6319578</v>
       </c>
       <c r="N67">
-        <v>57.9594355</v>
+        <v>57.7680422</v>
       </c>
       <c r="O67">
-        <v>15.649047585</v>
+        <v>15.597371394</v>
       </c>
       <c r="P67">
-        <v>42.31038791500001</v>
+        <v>42.170670806</v>
       </c>
       <c r="Q67">
-        <v>64.71038791500001</v>
+        <v>64.57067080600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.279993512161168</v>
+        <v>0.2860920839828657</v>
       </c>
       <c r="T67">
-        <v>2.805577929768566</v>
+        <v>2.878637248740173</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.658907198302778</v>
+        <v>5.573166180146675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1239148485541743</v>
+        <v>0.1235921178519399</v>
       </c>
       <c r="C68">
-        <v>173.6680444568533</v>
+        <v>171.6370524588891</v>
       </c>
       <c r="D68">
-        <v>344.6940444568534</v>
+        <v>346.1240524588892</v>
       </c>
       <c r="E68">
-        <v>-16.374</v>
+        <v>-12.91299999999998</v>
       </c>
       <c r="F68">
-        <v>228.426</v>
+        <v>231.887</v>
       </c>
       <c r="G68">
         <v>57.4</v>
@@ -6857,28 +6857,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M68">
-        <v>12.6319578</v>
+        <v>12.8233511</v>
       </c>
       <c r="N68">
-        <v>57.7680422</v>
+        <v>57.5766489</v>
       </c>
       <c r="O68">
-        <v>15.597371394</v>
+        <v>15.545695203</v>
       </c>
       <c r="P68">
-        <v>42.170670806</v>
+        <v>42.030953697</v>
       </c>
       <c r="Q68">
-        <v>64.57067080600001</v>
+        <v>64.43095369700001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2860920839828657</v>
+        <v>0.2925602662179997</v>
       </c>
       <c r="T68">
-        <v>2.878637248740173</v>
+        <v>2.956124405225211</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.573166180146675</v>
+        <v>5.489984595368366</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1235921178519399</v>
+        <v>0.1232693871497055</v>
       </c>
       <c r="C69">
-        <v>171.6370524588891</v>
+        <v>169.6179750378612</v>
       </c>
       <c r="D69">
-        <v>346.1240524588892</v>
+        <v>347.5659750378613</v>
       </c>
       <c r="E69">
-        <v>-12.91299999999998</v>
+        <v>-9.45199999999997</v>
       </c>
       <c r="F69">
-        <v>231.887</v>
+        <v>235.348</v>
       </c>
       <c r="G69">
         <v>57.4</v>
@@ -6939,28 +6939,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M69">
-        <v>12.8233511</v>
+        <v>13.0147444</v>
       </c>
       <c r="N69">
-        <v>57.5766489</v>
+        <v>57.3852556</v>
       </c>
       <c r="O69">
-        <v>15.545695203</v>
+        <v>15.494019012</v>
       </c>
       <c r="P69">
-        <v>42.030953697</v>
+        <v>41.891236588</v>
       </c>
       <c r="Q69">
-        <v>64.43095369700001</v>
+        <v>64.291236588</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2925602662179997</v>
+        <v>0.2994327098428295</v>
       </c>
       <c r="T69">
-        <v>2.956124405225211</v>
+        <v>3.038454508990563</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.489984595368366</v>
+        <v>5.409249527789419</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1232693871497055</v>
+        <v>0.122946656447471</v>
       </c>
       <c r="C70">
-        <v>169.6179750378612</v>
+        <v>167.6109617219524</v>
       </c>
       <c r="D70">
-        <v>347.5659750378613</v>
+        <v>349.0199617219524</v>
       </c>
       <c r="E70">
-        <v>-9.45199999999997</v>
+        <v>-5.990999999999985</v>
       </c>
       <c r="F70">
-        <v>235.348</v>
+        <v>238.809</v>
       </c>
       <c r="G70">
         <v>57.4</v>
@@ -7021,28 +7021,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M70">
-        <v>13.0147444</v>
+        <v>13.2061377</v>
       </c>
       <c r="N70">
-        <v>57.3852556</v>
+        <v>57.19386230000001</v>
       </c>
       <c r="O70">
-        <v>15.494019012</v>
+        <v>15.442342821</v>
       </c>
       <c r="P70">
-        <v>41.891236588</v>
+        <v>41.751519479</v>
       </c>
       <c r="Q70">
-        <v>64.291236588</v>
+        <v>64.151519479</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2994327098428295</v>
+        <v>0.3067485369273258</v>
       </c>
       <c r="T70">
-        <v>3.038454508990563</v>
+        <v>3.12609623235368</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.409249527789419</v>
+        <v>5.33085460709682</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.122946656447471</v>
+        <v>0.1226239257452365</v>
       </c>
       <c r="C71">
-        <v>167.6109617219524</v>
+        <v>165.6161645519653</v>
       </c>
       <c r="D71">
-        <v>349.0199617219524</v>
+        <v>350.4861645519653</v>
       </c>
       <c r="E71">
-        <v>-5.990999999999985</v>
+        <v>-2.529999999999973</v>
       </c>
       <c r="F71">
-        <v>238.809</v>
+        <v>242.27</v>
       </c>
       <c r="G71">
         <v>57.4</v>
@@ -7103,28 +7103,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M71">
-        <v>13.2061377</v>
+        <v>13.397531</v>
       </c>
       <c r="N71">
-        <v>57.19386230000001</v>
+        <v>57.002469</v>
       </c>
       <c r="O71">
-        <v>15.442342821</v>
+        <v>15.39066663</v>
       </c>
       <c r="P71">
-        <v>41.751519479</v>
+        <v>41.61180237000001</v>
       </c>
       <c r="Q71">
-        <v>64.151519479</v>
+        <v>64.01180237</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3067485369273258</v>
+        <v>0.3145520858174552</v>
       </c>
       <c r="T71">
-        <v>3.12609623235368</v>
+        <v>3.219580737274339</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.33085460709682</v>
+        <v>5.25469954128115</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1226239257452365</v>
+        <v>0.1223011950430021</v>
       </c>
       <c r="C72">
-        <v>165.6161645519653</v>
+        <v>163.6337381343221</v>
       </c>
       <c r="D72">
-        <v>350.4861645519653</v>
+        <v>351.9647381343221</v>
       </c>
       <c r="E72">
-        <v>-2.529999999999973</v>
+        <v>0.93100000000004</v>
       </c>
       <c r="F72">
-        <v>242.27</v>
+        <v>245.7310000000001</v>
       </c>
       <c r="G72">
         <v>57.4</v>
@@ -7185,28 +7185,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M72">
-        <v>13.397531</v>
+        <v>13.5889243</v>
       </c>
       <c r="N72">
-        <v>57.002469</v>
+        <v>56.8110757</v>
       </c>
       <c r="O72">
-        <v>15.39066663</v>
+        <v>15.338990439</v>
       </c>
       <c r="P72">
-        <v>41.61180237000001</v>
+        <v>41.472085261</v>
       </c>
       <c r="Q72">
-        <v>64.01180237</v>
+        <v>63.872085261</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3145520858174552</v>
+        <v>0.3228938104931107</v>
       </c>
       <c r="T72">
-        <v>3.219580737274339</v>
+        <v>3.319512449430905</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.25469954128115</v>
+        <v>5.18068968858705</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1223011950430021</v>
+        <v>0.1219784643407676</v>
       </c>
       <c r="C73">
-        <v>163.6337381343222</v>
+        <v>161.6638396954108</v>
       </c>
       <c r="D73">
-        <v>351.9647381343222</v>
+        <v>353.4558396954108</v>
       </c>
       <c r="E73">
-        <v>0.9309999999999832</v>
+        <v>4.391999999999996</v>
       </c>
       <c r="F73">
-        <v>245.731</v>
+        <v>249.192</v>
       </c>
       <c r="G73">
         <v>57.4</v>
@@ -7267,28 +7267,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M73">
-        <v>13.5889243</v>
+        <v>13.7803176</v>
       </c>
       <c r="N73">
-        <v>56.8110757</v>
+        <v>56.6196824</v>
       </c>
       <c r="O73">
-        <v>15.338990439</v>
+        <v>15.287314248</v>
       </c>
       <c r="P73">
-        <v>41.472085261</v>
+        <v>41.332368152</v>
       </c>
       <c r="Q73">
-        <v>63.872085261</v>
+        <v>63.732368152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3228938104931106</v>
+        <v>0.3318313726455987</v>
       </c>
       <c r="T73">
-        <v>3.319512449430903</v>
+        <v>3.426582141027224</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.180689688587051</v>
+        <v>5.108735665134453</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1219784643407676</v>
+        <v>0.1216557336385332</v>
       </c>
       <c r="C74">
-        <v>161.6638396954108</v>
+        <v>159.7066291373182</v>
       </c>
       <c r="D74">
-        <v>353.4558396954108</v>
+        <v>354.9596291373182</v>
       </c>
       <c r="E74">
-        <v>4.391999999999996</v>
+        <v>7.853000000000009</v>
       </c>
       <c r="F74">
-        <v>249.192</v>
+        <v>252.653</v>
       </c>
       <c r="G74">
         <v>57.4</v>
@@ -7349,28 +7349,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M74">
-        <v>13.7803176</v>
+        <v>13.9717109</v>
       </c>
       <c r="N74">
-        <v>56.6196824</v>
+        <v>56.4282891</v>
       </c>
       <c r="O74">
-        <v>15.287314248</v>
+        <v>15.235638057</v>
       </c>
       <c r="P74">
-        <v>41.332368152</v>
+        <v>41.192651043</v>
       </c>
       <c r="Q74">
-        <v>63.732368152</v>
+        <v>63.592651043</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3318313726455987</v>
+        <v>0.3414309764390118</v>
       </c>
       <c r="T74">
-        <v>3.426582141027224</v>
+        <v>3.541582920889938</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.108735665134453</v>
+        <v>5.038752984790144</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1216557336385332</v>
+        <v>0.1213330029362987</v>
       </c>
       <c r="C75">
-        <v>159.7066291373182</v>
+        <v>157.7622690949931</v>
       </c>
       <c r="D75">
-        <v>354.9596291373182</v>
+        <v>356.4762690949932</v>
       </c>
       <c r="E75">
-        <v>7.853000000000009</v>
+        <v>11.31400000000002</v>
       </c>
       <c r="F75">
-        <v>252.653</v>
+        <v>256.114</v>
       </c>
       <c r="G75">
         <v>57.4</v>
@@ -7431,28 +7431,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M75">
-        <v>13.9717109</v>
+        <v>14.1631042</v>
       </c>
       <c r="N75">
-        <v>56.4282891</v>
+        <v>56.2368958</v>
       </c>
       <c r="O75">
-        <v>15.235638057</v>
+        <v>15.183961866</v>
       </c>
       <c r="P75">
-        <v>41.192651043</v>
+        <v>41.052933934</v>
       </c>
       <c r="Q75">
-        <v>63.592651043</v>
+        <v>63.45293393399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3414309764390118</v>
+        <v>0.3517690112934567</v>
       </c>
       <c r="T75">
-        <v>3.541582920889938</v>
+        <v>3.665429914588246</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.038752984790144</v>
+        <v>4.970661728238926</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1213330029362987</v>
+        <v>0.1210102722340643</v>
       </c>
       <c r="C76">
-        <v>157.7622690949931</v>
+        <v>155.8309249948801</v>
       </c>
       <c r="D76">
-        <v>356.4762690949932</v>
+        <v>358.0059249948802</v>
       </c>
       <c r="E76">
-        <v>11.31400000000002</v>
+        <v>14.77500000000003</v>
       </c>
       <c r="F76">
-        <v>256.114</v>
+        <v>259.575</v>
       </c>
       <c r="G76">
         <v>57.4</v>
@@ -7513,28 +7513,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M76">
-        <v>14.1631042</v>
+        <v>14.3544975</v>
       </c>
       <c r="N76">
-        <v>56.2368958</v>
+        <v>56.0455025</v>
       </c>
       <c r="O76">
-        <v>15.183961866</v>
+        <v>15.132285675</v>
       </c>
       <c r="P76">
-        <v>41.052933934</v>
+        <v>40.91321682500001</v>
       </c>
       <c r="Q76">
-        <v>63.45293393399999</v>
+        <v>63.313216825</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3517690112934567</v>
+        <v>0.3629340889362571</v>
       </c>
       <c r="T76">
-        <v>3.665429914588246</v>
+        <v>3.799184667782418</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.970661728238926</v>
+        <v>4.904386238529074</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1210102722340643</v>
+        <v>0.1206875415318298</v>
       </c>
       <c r="C77">
-        <v>155.8309249948801</v>
+        <v>153.9127651150699</v>
       </c>
       <c r="D77">
-        <v>358.0059249948802</v>
+        <v>359.54876511507</v>
       </c>
       <c r="E77">
-        <v>14.77500000000003</v>
+        <v>18.23599999999999</v>
       </c>
       <c r="F77">
-        <v>259.575</v>
+        <v>263.036</v>
       </c>
       <c r="G77">
         <v>57.4</v>
@@ -7595,28 +7595,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M77">
-        <v>14.3544975</v>
+        <v>14.5458908</v>
       </c>
       <c r="N77">
-        <v>56.0455025</v>
+        <v>55.8541092</v>
       </c>
       <c r="O77">
-        <v>15.132285675</v>
+        <v>15.080609484</v>
       </c>
       <c r="P77">
-        <v>40.91321682500001</v>
+        <v>40.773499716</v>
       </c>
       <c r="Q77">
-        <v>63.313216825</v>
+        <v>63.173499716</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3629340889362571</v>
+        <v>0.3750295897159577</v>
       </c>
       <c r="T77">
-        <v>3.799184667782418</v>
+        <v>3.944085650409439</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.904386238529074</v>
+        <v>4.839854840653691</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1206875415318298</v>
+        <v>0.1203648108295954</v>
       </c>
       <c r="C78">
-        <v>153.9127651150699</v>
+        <v>152.0079606470119</v>
       </c>
       <c r="D78">
-        <v>359.54876511507</v>
+        <v>361.104960647012</v>
       </c>
       <c r="E78">
-        <v>18.23599999999999</v>
+        <v>21.697</v>
       </c>
       <c r="F78">
-        <v>263.036</v>
+        <v>266.497</v>
       </c>
       <c r="G78">
         <v>57.4</v>
@@ -7677,28 +7677,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M78">
-        <v>14.5458908</v>
+        <v>14.7372841</v>
       </c>
       <c r="N78">
-        <v>55.8541092</v>
+        <v>55.6627159</v>
       </c>
       <c r="O78">
-        <v>15.080609484</v>
+        <v>15.028933293</v>
       </c>
       <c r="P78">
-        <v>40.773499716</v>
+        <v>40.633782607</v>
       </c>
       <c r="Q78">
-        <v>63.173499716</v>
+        <v>63.033782607</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3750295897159577</v>
+        <v>0.3881768731721539</v>
       </c>
       <c r="T78">
-        <v>3.944085650409439</v>
+        <v>4.101586718482286</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.839854840653691</v>
+        <v>4.776999582982864</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1203648108295954</v>
+        <v>0.1200420801273609</v>
       </c>
       <c r="C79">
-        <v>152.0079606470119</v>
+        <v>150.1166857588357</v>
       </c>
       <c r="D79">
-        <v>361.104960647012</v>
+        <v>362.6746857588358</v>
       </c>
       <c r="E79">
-        <v>21.697</v>
+        <v>25.15800000000002</v>
       </c>
       <c r="F79">
-        <v>266.497</v>
+        <v>269.958</v>
       </c>
       <c r="G79">
         <v>57.4</v>
@@ -7759,28 +7759,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M79">
-        <v>14.7372841</v>
+        <v>14.9286774</v>
       </c>
       <c r="N79">
-        <v>55.6627159</v>
+        <v>55.47132260000001</v>
       </c>
       <c r="O79">
-        <v>15.028933293</v>
+        <v>14.977257102</v>
       </c>
       <c r="P79">
-        <v>40.633782607</v>
+        <v>40.494065498</v>
       </c>
       <c r="Q79">
-        <v>63.033782607</v>
+        <v>62.894065498</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3881768731721539</v>
+        <v>0.402519364215277</v>
       </c>
       <c r="T79">
-        <v>4.101586718482286</v>
+        <v>4.273406065470848</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.776999582982864</v>
+        <v>4.715755998585649</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1200420801273609</v>
+        <v>0.1197193494251265</v>
       </c>
       <c r="C80">
-        <v>150.1166857588357</v>
+        <v>148.2391176603322</v>
       </c>
       <c r="D80">
-        <v>362.6746857588358</v>
+        <v>364.2581176603322</v>
       </c>
       <c r="E80">
-        <v>25.15800000000002</v>
+        <v>28.61900000000003</v>
       </c>
       <c r="F80">
-        <v>269.958</v>
+        <v>273.419</v>
       </c>
       <c r="G80">
         <v>57.4</v>
@@ -7841,28 +7841,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M80">
-        <v>14.9286774</v>
+        <v>15.1200707</v>
       </c>
       <c r="N80">
-        <v>55.47132260000001</v>
+        <v>55.27992930000001</v>
       </c>
       <c r="O80">
-        <v>14.977257102</v>
+        <v>14.925580911</v>
       </c>
       <c r="P80">
-        <v>40.494065498</v>
+        <v>40.354348389</v>
       </c>
       <c r="Q80">
-        <v>62.894065498</v>
+        <v>62.754348389</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.402519364215277</v>
+        <v>0.4182278067863167</v>
       </c>
       <c r="T80">
-        <v>4.273406065470848</v>
+        <v>4.461589159791654</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.715755998585649</v>
+        <v>4.656062884679501</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1197193494251265</v>
+        <v>0.119396618722892</v>
       </c>
       <c r="C81">
-        <v>148.2391176603322</v>
+        <v>146.3754366696436</v>
       </c>
       <c r="D81">
-        <v>364.2581176603322</v>
+        <v>365.8554366696437</v>
       </c>
       <c r="E81">
-        <v>28.61900000000003</v>
+        <v>32.08000000000004</v>
       </c>
       <c r="F81">
-        <v>273.419</v>
+        <v>276.8800000000001</v>
       </c>
       <c r="G81">
         <v>57.4</v>
@@ -7923,28 +7923,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M81">
-        <v>15.1200707</v>
+        <v>15.311464</v>
       </c>
       <c r="N81">
-        <v>55.27992930000001</v>
+        <v>55.088536</v>
       </c>
       <c r="O81">
-        <v>14.925580911</v>
+        <v>14.87390472</v>
       </c>
       <c r="P81">
-        <v>40.354348389</v>
+        <v>40.21463128000001</v>
       </c>
       <c r="Q81">
-        <v>62.754348389</v>
+        <v>62.61463128</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4182278067863167</v>
+        <v>0.4355070936144602</v>
       </c>
       <c r="T81">
-        <v>4.461589159791654</v>
+        <v>4.668590563544539</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.656062884679501</v>
+        <v>4.597862098621007</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.119396618722892</v>
+        <v>0.1190738880206576</v>
       </c>
       <c r="C82">
-        <v>146.3754366696436</v>
+        <v>144.5258262817166</v>
       </c>
       <c r="D82">
-        <v>365.8554366696437</v>
+        <v>367.4668262817167</v>
       </c>
       <c r="E82">
-        <v>32.08000000000004</v>
+        <v>35.54100000000005</v>
       </c>
       <c r="F82">
-        <v>276.8800000000001</v>
+        <v>280.3410000000001</v>
       </c>
       <c r="G82">
         <v>57.4</v>
@@ -8005,28 +8005,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M82">
-        <v>15.311464</v>
+        <v>15.5028573</v>
       </c>
       <c r="N82">
-        <v>55.088536</v>
+        <v>54.8971427</v>
       </c>
       <c r="O82">
-        <v>14.87390472</v>
+        <v>14.822228529</v>
       </c>
       <c r="P82">
-        <v>40.21463128000001</v>
+        <v>40.074914171</v>
       </c>
       <c r="Q82">
-        <v>62.61463128</v>
+        <v>62.474914171</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4355070936144602</v>
+        <v>0.4546052527403031</v>
       </c>
       <c r="T82">
-        <v>4.668590563544539</v>
+        <v>4.897381588745097</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.597862098621007</v>
+        <v>4.541098369008401</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1190738880206576</v>
+        <v>0.1202476573184231</v>
       </c>
       <c r="C83">
-        <v>144.5258262817166</v>
+        <v>135.2712084007401</v>
       </c>
       <c r="D83">
-        <v>367.4668262817167</v>
+        <v>361.6732084007402</v>
       </c>
       <c r="E83">
-        <v>35.54100000000005</v>
+        <v>39.00200000000001</v>
       </c>
       <c r="F83">
-        <v>280.3410000000001</v>
+        <v>283.802</v>
       </c>
       <c r="G83">
         <v>57.4</v>
@@ -8087,45 +8087,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M83">
-        <v>15.5028573</v>
+        <v>16.4037556</v>
       </c>
       <c r="N83">
-        <v>54.8971427</v>
+        <v>53.9962444</v>
       </c>
       <c r="O83">
-        <v>14.822228529</v>
+        <v>14.578985988</v>
       </c>
       <c r="P83">
-        <v>40.074914171</v>
+        <v>39.417258412</v>
       </c>
       <c r="Q83">
-        <v>62.474914171</v>
+        <v>61.817258412</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4546052527403031</v>
+        <v>0.4758254295467953</v>
       </c>
       <c r="T83">
-        <v>4.897381588745097</v>
+        <v>5.151593838967941</v>
       </c>
       <c r="U83">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.541098369008401</v>
+        <v>4.29170012750007</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1202476573184231</v>
+        <v>0.1199431766161887</v>
       </c>
       <c r="C84">
-        <v>135.2712084007401</v>
+        <v>133.2954767355904</v>
       </c>
       <c r="D84">
-        <v>361.6732084007402</v>
+        <v>363.1584767355905</v>
       </c>
       <c r="E84">
-        <v>39.00200000000001</v>
+        <v>42.46300000000002</v>
       </c>
       <c r="F84">
-        <v>283.802</v>
+        <v>287.263</v>
       </c>
       <c r="G84">
         <v>57.4</v>
@@ -8169,28 +8169,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M84">
-        <v>16.4037556</v>
+        <v>16.6038014</v>
       </c>
       <c r="N84">
-        <v>53.9962444</v>
+        <v>53.7961986</v>
       </c>
       <c r="O84">
-        <v>14.578985988</v>
+        <v>14.524973622</v>
       </c>
       <c r="P84">
-        <v>39.417258412</v>
+        <v>39.271224978</v>
       </c>
       <c r="Q84">
-        <v>61.817258412</v>
+        <v>61.671224978</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4758254295467953</v>
+        <v>0.4995420977422866</v>
       </c>
       <c r="T84">
-        <v>5.151593838967941</v>
+        <v>5.435713412746413</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.29170012750007</v>
+        <v>4.239992897048262</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1199431766161887</v>
+        <v>0.1196386959139542</v>
       </c>
       <c r="C85">
-        <v>133.2954767355904</v>
+        <v>131.3319943535573</v>
       </c>
       <c r="D85">
-        <v>363.1584767355905</v>
+        <v>364.6559943535574</v>
       </c>
       <c r="E85">
-        <v>42.46300000000002</v>
+        <v>45.92400000000004</v>
       </c>
       <c r="F85">
-        <v>287.263</v>
+        <v>290.724</v>
       </c>
       <c r="G85">
         <v>57.4</v>
@@ -8251,28 +8251,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M85">
-        <v>16.6038014</v>
+        <v>16.8038472</v>
       </c>
       <c r="N85">
-        <v>53.7961986</v>
+        <v>53.5961528</v>
       </c>
       <c r="O85">
-        <v>14.524973622</v>
+        <v>14.470961256</v>
       </c>
       <c r="P85">
-        <v>39.271224978</v>
+        <v>39.125191544</v>
       </c>
       <c r="Q85">
-        <v>61.671224978</v>
+        <v>61.52519154399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4995420977422866</v>
+        <v>0.5262233494622143</v>
       </c>
       <c r="T85">
-        <v>5.435713412746413</v>
+        <v>5.755347933247194</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.239992897048262</v>
+        <v>4.189516791131021</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1196386959139543</v>
+        <v>0.1193342152117198</v>
       </c>
       <c r="C86">
-        <v>131.3319943535572</v>
+        <v>129.3809134152499</v>
       </c>
       <c r="D86">
-        <v>364.6559943535572</v>
+        <v>366.1659134152499</v>
       </c>
       <c r="E86">
-        <v>45.92399999999998</v>
+        <v>49.38499999999999</v>
       </c>
       <c r="F86">
-        <v>290.724</v>
+        <v>294.185</v>
       </c>
       <c r="G86">
         <v>57.4</v>
@@ -8333,28 +8333,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M86">
-        <v>16.8038472</v>
+        <v>17.003893</v>
       </c>
       <c r="N86">
-        <v>53.59615280000001</v>
+        <v>53.396107</v>
       </c>
       <c r="O86">
-        <v>14.470961256</v>
+        <v>14.41694889</v>
       </c>
       <c r="P86">
-        <v>39.125191544</v>
+        <v>38.97915811</v>
       </c>
       <c r="Q86">
-        <v>61.525191544</v>
+        <v>61.37915811</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5262233494622139</v>
+        <v>0.5564621014114651</v>
       </c>
       <c r="T86">
-        <v>5.755347933247189</v>
+        <v>6.117600389814739</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.189516791131021</v>
+        <v>4.140228358294186</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1193342152117198</v>
+        <v>0.1190297345094853</v>
       </c>
       <c r="C87">
-        <v>129.3809134152499</v>
+        <v>127.4423886119413</v>
       </c>
       <c r="D87">
-        <v>366.1659134152499</v>
+        <v>367.6883886119413</v>
       </c>
       <c r="E87">
-        <v>49.38499999999999</v>
+        <v>52.846</v>
       </c>
       <c r="F87">
-        <v>294.185</v>
+        <v>297.646</v>
       </c>
       <c r="G87">
         <v>57.4</v>
@@ -8415,28 +8415,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M87">
-        <v>17.003893</v>
+        <v>17.2039388</v>
       </c>
       <c r="N87">
-        <v>53.396107</v>
+        <v>53.1960612</v>
       </c>
       <c r="O87">
-        <v>14.41694889</v>
+        <v>14.362936524</v>
       </c>
       <c r="P87">
-        <v>38.97915811</v>
+        <v>38.833124676</v>
       </c>
       <c r="Q87">
-        <v>61.37915811</v>
+        <v>61.233124676</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5564621014114651</v>
+        <v>0.5910206750677524</v>
       </c>
       <c r="T87">
-        <v>6.117600389814739</v>
+        <v>6.531603197320512</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.140228358294186</v>
+        <v>4.092086168081463</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1190297345094853</v>
+        <v>0.1187252538072509</v>
       </c>
       <c r="C88">
-        <v>127.4423886119413</v>
+        <v>125.5165772184002</v>
       </c>
       <c r="D88">
-        <v>367.6883886119413</v>
+        <v>369.2235772184003</v>
       </c>
       <c r="E88">
-        <v>52.846</v>
+        <v>56.30700000000002</v>
       </c>
       <c r="F88">
-        <v>297.646</v>
+        <v>301.107</v>
       </c>
       <c r="G88">
         <v>57.4</v>
@@ -8497,28 +8497,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M88">
-        <v>17.2039388</v>
+        <v>17.4039846</v>
       </c>
       <c r="N88">
-        <v>53.1960612</v>
+        <v>52.9960154</v>
       </c>
       <c r="O88">
-        <v>14.362936524</v>
+        <v>14.308924158</v>
       </c>
       <c r="P88">
-        <v>38.833124676</v>
+        <v>38.687091242</v>
       </c>
       <c r="Q88">
-        <v>61.233124676</v>
+        <v>61.087091242</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5910206750677524</v>
+        <v>0.6308959523634683</v>
       </c>
       <c r="T88">
-        <v>6.531603197320512</v>
+        <v>7.009298744442556</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.092086168081463</v>
+        <v>4.045050694885124</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1187252538072509</v>
+        <v>0.1206691731050164</v>
       </c>
       <c r="C89">
-        <v>125.5165772184002</v>
+        <v>112.468976923802</v>
       </c>
       <c r="D89">
-        <v>369.2235772184003</v>
+        <v>359.6369769238021</v>
       </c>
       <c r="E89">
-        <v>56.30700000000002</v>
+        <v>59.76800000000003</v>
       </c>
       <c r="F89">
-        <v>301.107</v>
+        <v>304.568</v>
       </c>
       <c r="G89">
         <v>57.4</v>
@@ -8579,45 +8579,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M89">
-        <v>17.4039846</v>
+        <v>18.6700184</v>
       </c>
       <c r="N89">
-        <v>52.9960154</v>
+        <v>51.7299816</v>
       </c>
       <c r="O89">
-        <v>14.308924158</v>
+        <v>13.967095032</v>
       </c>
       <c r="P89">
-        <v>38.687091242</v>
+        <v>37.762886568</v>
       </c>
       <c r="Q89">
-        <v>61.087091242</v>
+        <v>60.162886568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6308959523634683</v>
+        <v>0.6774171092084703</v>
       </c>
       <c r="T89">
-        <v>7.009298744442556</v>
+        <v>7.566610216084942</v>
       </c>
       <c r="U89">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.045050694885124</v>
+        <v>3.770751506061718</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1206691731050164</v>
+        <v>0.120390242402782</v>
       </c>
       <c r="C90">
-        <v>112.468976923802</v>
+        <v>110.3528417652533</v>
       </c>
       <c r="D90">
-        <v>359.6369769238021</v>
+        <v>360.9818417652534</v>
       </c>
       <c r="E90">
-        <v>59.76800000000003</v>
+        <v>63.22900000000004</v>
       </c>
       <c r="F90">
-        <v>304.568</v>
+        <v>308.0290000000001</v>
       </c>
       <c r="G90">
         <v>57.4</v>
@@ -8661,28 +8661,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M90">
-        <v>18.6700184</v>
+        <v>18.8821777</v>
       </c>
       <c r="N90">
-        <v>51.7299816</v>
+        <v>51.51782230000001</v>
       </c>
       <c r="O90">
-        <v>13.967095032</v>
+        <v>13.909812021</v>
       </c>
       <c r="P90">
-        <v>37.762886568</v>
+        <v>37.60801027900001</v>
       </c>
       <c r="Q90">
-        <v>60.162886568</v>
+        <v>60.008010279</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6774171092084703</v>
+        <v>0.732396658207109</v>
       </c>
       <c r="T90">
-        <v>7.566610216084942</v>
+        <v>8.225251046207761</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.770751506061718</v>
+        <v>3.728383511611587</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.120390242402782</v>
+        <v>0.1201113117005475</v>
       </c>
       <c r="C91">
-        <v>110.3528417652533</v>
+        <v>108.2468026226691</v>
       </c>
       <c r="D91">
-        <v>360.9818417652534</v>
+        <v>362.3368026226692</v>
       </c>
       <c r="E91">
-        <v>63.22900000000004</v>
+        <v>66.69</v>
       </c>
       <c r="F91">
-        <v>308.0290000000001</v>
+        <v>311.49</v>
       </c>
       <c r="G91">
         <v>57.4</v>
@@ -8743,28 +8743,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M91">
-        <v>18.8821777</v>
+        <v>19.094337</v>
       </c>
       <c r="N91">
-        <v>51.51782230000001</v>
+        <v>51.30566300000001</v>
       </c>
       <c r="O91">
-        <v>13.909812021</v>
+        <v>13.85252901</v>
       </c>
       <c r="P91">
-        <v>37.60801027900001</v>
+        <v>37.45313399</v>
       </c>
       <c r="Q91">
-        <v>60.008010279</v>
+        <v>59.85313399</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.732396658207109</v>
+        <v>0.7983721170054754</v>
       </c>
       <c r="T91">
-        <v>8.225251046207761</v>
+        <v>9.015620042355144</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.728383511611587</v>
+        <v>3.686957028149237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1201113117005475</v>
+        <v>0.1198323809983131</v>
       </c>
       <c r="C92">
-        <v>108.2468026226691</v>
+        <v>106.1509736118776</v>
       </c>
       <c r="D92">
-        <v>362.3368026226692</v>
+        <v>363.7019736118776</v>
       </c>
       <c r="E92">
-        <v>66.69</v>
+        <v>70.15100000000001</v>
       </c>
       <c r="F92">
-        <v>311.49</v>
+        <v>314.951</v>
       </c>
       <c r="G92">
         <v>57.4</v>
@@ -8825,28 +8825,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M92">
-        <v>19.094337</v>
+        <v>19.3064963</v>
       </c>
       <c r="N92">
-        <v>51.30566300000001</v>
+        <v>51.0935037</v>
       </c>
       <c r="O92">
-        <v>13.85252901</v>
+        <v>13.795245999</v>
       </c>
       <c r="P92">
-        <v>37.45313399</v>
+        <v>37.298257701</v>
       </c>
       <c r="Q92">
-        <v>59.85313399</v>
+        <v>59.698257701</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7983721170054754</v>
+        <v>0.8790087888701457</v>
       </c>
       <c r="T92">
-        <v>9.015620042355144</v>
+        <v>9.981626593201947</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.686957028149237</v>
+        <v>3.646441016850893</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1198323809983131</v>
+        <v>0.1195534502960786</v>
       </c>
       <c r="C93">
-        <v>106.1509736118776</v>
+        <v>104.0654705750211</v>
       </c>
       <c r="D93">
-        <v>363.7019736118776</v>
+        <v>365.0774705750212</v>
       </c>
       <c r="E93">
-        <v>70.15100000000001</v>
+        <v>73.61200000000002</v>
       </c>
       <c r="F93">
-        <v>314.951</v>
+        <v>318.412</v>
       </c>
       <c r="G93">
         <v>57.4</v>
@@ -8907,28 +8907,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M93">
-        <v>19.3064963</v>
+        <v>19.5186556</v>
       </c>
       <c r="N93">
-        <v>51.0935037</v>
+        <v>50.8813444</v>
       </c>
       <c r="O93">
-        <v>13.795245999</v>
+        <v>13.737962988</v>
       </c>
       <c r="P93">
-        <v>37.298257701</v>
+        <v>37.143381412</v>
       </c>
       <c r="Q93">
-        <v>59.698257701</v>
+        <v>59.543381412</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8790087888701457</v>
+        <v>0.9798046287009835</v>
       </c>
       <c r="T93">
-        <v>9.981626593201947</v>
+        <v>11.18913478176045</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.646441016850893</v>
+        <v>3.606805788406861</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1195534502960786</v>
+        <v>0.1192745195938442</v>
       </c>
       <c r="C94">
-        <v>104.0654705750211</v>
+        <v>101.9904111133244</v>
       </c>
       <c r="D94">
-        <v>365.0774705750212</v>
+        <v>366.4634111133245</v>
       </c>
       <c r="E94">
-        <v>73.61200000000002</v>
+        <v>77.07300000000004</v>
       </c>
       <c r="F94">
-        <v>318.412</v>
+        <v>321.873</v>
       </c>
       <c r="G94">
         <v>57.4</v>
@@ -8989,28 +8989,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M94">
-        <v>19.5186556</v>
+        <v>19.7308149</v>
       </c>
       <c r="N94">
-        <v>50.8813444</v>
+        <v>50.66918510000001</v>
       </c>
       <c r="O94">
-        <v>13.737962988</v>
+        <v>13.680679977</v>
       </c>
       <c r="P94">
-        <v>37.143381412</v>
+        <v>36.988505123</v>
       </c>
       <c r="Q94">
-        <v>59.543381412</v>
+        <v>59.388505123</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9798046287009835</v>
+        <v>1.109399279912061</v>
       </c>
       <c r="T94">
-        <v>11.18913478176045</v>
+        <v>12.7416453099071</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.606805788406861</v>
+        <v>3.568022930467003</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1192745195938442</v>
+        <v>0.1189955888916097</v>
       </c>
       <c r="C95">
-        <v>101.9904111133244</v>
+        <v>99.92591462061142</v>
       </c>
       <c r="D95">
-        <v>366.4634111133245</v>
+        <v>367.8599146206115</v>
       </c>
       <c r="E95">
-        <v>77.07300000000004</v>
+        <v>80.53400000000005</v>
       </c>
       <c r="F95">
-        <v>321.873</v>
+        <v>325.3340000000001</v>
       </c>
       <c r="G95">
         <v>57.4</v>
@@ -9071,28 +9071,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M95">
-        <v>19.7308149</v>
+        <v>19.94297420000001</v>
       </c>
       <c r="N95">
-        <v>50.66918510000001</v>
+        <v>50.4570258</v>
       </c>
       <c r="O95">
-        <v>13.680679977</v>
+        <v>13.623396966</v>
       </c>
       <c r="P95">
-        <v>36.988505123</v>
+        <v>36.833628834</v>
       </c>
       <c r="Q95">
-        <v>59.388505123</v>
+        <v>59.23362883399999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.109399279912061</v>
+        <v>1.282192148193497</v>
       </c>
       <c r="T95">
-        <v>12.7416453099071</v>
+        <v>14.81165934743596</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.568022930467003</v>
+        <v>3.530065239717353</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1189955888916097</v>
+        <v>0.1206584581893753</v>
       </c>
       <c r="C96">
-        <v>99.92591462061142</v>
+        <v>88.29345380380153</v>
       </c>
       <c r="D96">
-        <v>367.8599146206115</v>
+        <v>359.6884538038016</v>
       </c>
       <c r="E96">
-        <v>80.53400000000005</v>
+        <v>83.99500000000006</v>
       </c>
       <c r="F96">
-        <v>325.3340000000001</v>
+        <v>328.7950000000001</v>
       </c>
       <c r="G96">
         <v>57.4</v>
@@ -9153,45 +9153,45 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M96">
-        <v>19.94297420000001</v>
+        <v>21.07575950000001</v>
       </c>
       <c r="N96">
-        <v>50.4570258</v>
+        <v>49.3242405</v>
       </c>
       <c r="O96">
-        <v>13.623396966</v>
+        <v>13.317544935</v>
       </c>
       <c r="P96">
-        <v>36.833628834</v>
+        <v>36.006695565</v>
       </c>
       <c r="Q96">
-        <v>59.23362883399999</v>
+        <v>58.406695565</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.282192148193497</v>
+        <v>1.524102163787508</v>
       </c>
       <c r="T96">
-        <v>14.81165934743596</v>
+        <v>17.70967899997638</v>
       </c>
       <c r="U96">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V96">
         <v>0.27</v>
       </c>
       <c r="W96">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.530065239717353</v>
+        <v>3.340330392363795</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1206584581893753</v>
+        <v>0.1203999674871408</v>
       </c>
       <c r="C97">
-        <v>88.29345380380153</v>
+        <v>86.0787830468459</v>
       </c>
       <c r="D97">
-        <v>359.6884538038016</v>
+        <v>360.934783046846</v>
       </c>
       <c r="E97">
-        <v>83.99500000000006</v>
+        <v>87.45600000000002</v>
       </c>
       <c r="F97">
-        <v>328.7950000000001</v>
+        <v>332.256</v>
       </c>
       <c r="G97">
         <v>57.4</v>
@@ -9235,28 +9235,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M97">
-        <v>21.07575950000001</v>
+        <v>21.2976096</v>
       </c>
       <c r="N97">
-        <v>49.3242405</v>
+        <v>49.1023904</v>
       </c>
       <c r="O97">
-        <v>13.317544935</v>
+        <v>13.257645408</v>
       </c>
       <c r="P97">
-        <v>36.006695565</v>
+        <v>35.844744992</v>
       </c>
       <c r="Q97">
-        <v>58.406695565</v>
+        <v>58.244744992</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.524102163787508</v>
+        <v>1.886967187178524</v>
       </c>
       <c r="T97">
-        <v>17.70967899997638</v>
+        <v>22.05670847878699</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.340330392363795</v>
+        <v>3.305535284110006</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1203999674871409</v>
+        <v>0.1201414767849064</v>
       </c>
       <c r="C98">
-        <v>86.07878304684579</v>
+        <v>83.87277944408675</v>
       </c>
       <c r="D98">
-        <v>360.9347830468458</v>
+        <v>362.1897794440868</v>
       </c>
       <c r="E98">
-        <v>87.45600000000002</v>
+        <v>90.91699999999997</v>
       </c>
       <c r="F98">
-        <v>332.256</v>
+        <v>335.717</v>
       </c>
       <c r="G98">
         <v>57.4</v>
@@ -9317,28 +9317,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M98">
-        <v>21.2976096</v>
+        <v>21.5194597</v>
       </c>
       <c r="N98">
-        <v>49.1023904</v>
+        <v>48.88054030000001</v>
       </c>
       <c r="O98">
-        <v>13.257645408</v>
+        <v>13.197745881</v>
       </c>
       <c r="P98">
-        <v>35.844744992</v>
+        <v>35.682794419</v>
       </c>
       <c r="Q98">
-        <v>58.244744992</v>
+        <v>58.082794419</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.88696718717852</v>
+        <v>2.491742226163544</v>
       </c>
       <c r="T98">
-        <v>22.05670847878694</v>
+        <v>29.30175761013794</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.305535284110006</v>
+        <v>3.271457600768667</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1201414767849064</v>
+        <v>0.1198829860826719</v>
       </c>
       <c r="C99">
-        <v>83.87277944408675</v>
+        <v>81.67553371994916</v>
       </c>
       <c r="D99">
-        <v>362.1897794440868</v>
+        <v>363.4535337199492</v>
       </c>
       <c r="E99">
-        <v>90.91699999999997</v>
+        <v>94.37799999999999</v>
       </c>
       <c r="F99">
-        <v>335.717</v>
+        <v>339.178</v>
       </c>
       <c r="G99">
         <v>57.4</v>
@@ -9399,28 +9399,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M99">
-        <v>21.5194597</v>
+        <v>21.7413098</v>
       </c>
       <c r="N99">
-        <v>48.88054030000001</v>
+        <v>48.65869020000001</v>
       </c>
       <c r="O99">
-        <v>13.197745881</v>
+        <v>13.137846354</v>
       </c>
       <c r="P99">
-        <v>35.682794419</v>
+        <v>35.52084384600001</v>
       </c>
       <c r="Q99">
-        <v>58.082794419</v>
+        <v>57.920843846</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.491742226163544</v>
+        <v>3.701292304133594</v>
       </c>
       <c r="T99">
-        <v>29.30175761013794</v>
+        <v>43.79185587283994</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.271457600768667</v>
+        <v>3.23807538035266</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1198829860826719</v>
+        <v>0.1196244953804375</v>
       </c>
       <c r="C100">
-        <v>81.67553371994916</v>
+        <v>79.48713786951657</v>
       </c>
       <c r="D100">
-        <v>363.4535337199492</v>
+        <v>364.7261378695166</v>
       </c>
       <c r="E100">
-        <v>94.37799999999999</v>
+        <v>97.839</v>
       </c>
       <c r="F100">
-        <v>339.178</v>
+        <v>342.639</v>
       </c>
       <c r="G100">
         <v>57.4</v>
@@ -9481,28 +9481,28 @@
         <v>70.40000000000001</v>
       </c>
       <c r="M100">
-        <v>21.7413098</v>
+        <v>21.9631599</v>
       </c>
       <c r="N100">
-        <v>48.65869020000001</v>
+        <v>48.4368401</v>
       </c>
       <c r="O100">
-        <v>13.137846354</v>
+        <v>13.077946827</v>
       </c>
       <c r="P100">
-        <v>35.52084384600001</v>
+        <v>35.35889327300001</v>
       </c>
       <c r="Q100">
-        <v>57.920843846</v>
+        <v>57.75889327300001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.701292304133594</v>
+        <v>7.329942538043743</v>
       </c>
       <c r="T100">
-        <v>43.79185587283994</v>
+        <v>87.26215066094593</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.23807538035266</v>
+        <v>3.205367548227885</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1196244953804375</v>
-      </c>
-      <c r="C101">
-        <v>79.48713786951657</v>
-      </c>
-      <c r="D101">
-        <v>364.7261378695166</v>
-      </c>
-      <c r="E101">
-        <v>97.839</v>
-      </c>
-      <c r="F101">
-        <v>342.639</v>
-      </c>
-      <c r="G101">
-        <v>57.4</v>
-      </c>
-      <c r="H101">
-        <v>101.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>92.8</v>
-      </c>
-      <c r="K101">
-        <v>22.4</v>
-      </c>
-      <c r="L101">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="M101">
-        <v>21.9631599</v>
-      </c>
-      <c r="N101">
-        <v>48.4368401</v>
-      </c>
-      <c r="O101">
-        <v>13.077946827</v>
-      </c>
-      <c r="P101">
-        <v>35.35889327300001</v>
-      </c>
-      <c r="Q101">
-        <v>57.75889327300001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.329942538043743</v>
-      </c>
-      <c r="T101">
-        <v>87.26215066094593</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.046793</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.205367548227885</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
